--- a/Project Dataset.xlsx
+++ b/Project Dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivam\OneDrive\Documents\0. MCA\Term - 1\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F391E60D-34DC-494B-8140-81962C04A231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E95B8A1-1D64-439E-ABA1-440DCE6DB2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,12 @@
   </si>
   <si>
     <t>Boring day.</t>
+  </si>
+  <si>
+    <t>Wasn't fit today.</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1438,26 +1444,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+      <c r="A15" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="14">
+        <v>500</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>300</v>
+      </c>
+      <c r="E15" s="14">
+        <v>120</v>
+      </c>
+      <c r="F15" s="14">
+        <v>300</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>190</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" ref="I15" si="2">IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
+        <v>1440</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" ref="J15" si="3">IF(I15="","",1440-I15)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
@@ -2657,11 +2687,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2679,11 +2709,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2701,11 +2731,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2723,11 +2753,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2745,11 +2775,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2767,11 +2797,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2789,11 +2819,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2811,11 +2841,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2833,11 +2863,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2855,11 +2885,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2877,11 +2907,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2899,11 +2929,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2921,11 +2951,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -2943,11 +2973,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -2965,11 +2995,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -2987,11 +3017,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3009,11 +3039,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3031,11 +3061,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3053,11 +3083,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3075,11 +3105,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3097,11 +3127,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3119,11 +3149,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3141,11 +3171,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3163,11 +3193,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3185,11 +3215,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3207,11 +3237,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3229,11 +3259,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3251,11 +3281,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3273,11 +3303,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3295,11 +3325,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3317,11 +3347,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3339,11 +3369,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3361,11 +3391,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3383,11 +3413,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3405,11 +3435,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3427,11 +3457,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3449,11 +3479,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3471,11 +3501,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3493,11 +3523,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3515,11 +3545,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3537,11 +3567,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3559,11 +3589,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3581,11 +3611,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3603,11 +3633,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3625,11 +3655,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3647,11 +3677,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3669,11 +3699,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3691,11 +3721,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3713,11 +3743,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3735,11 +3765,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3757,11 +3787,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3779,11 +3809,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3801,11 +3831,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3823,11 +3853,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3845,11 +3875,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3867,11 +3897,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3889,11 +3919,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3911,11 +3941,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3933,11 +3963,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -3955,11 +3985,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -3977,11 +4007,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -3999,11 +4029,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4021,11 +4051,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4043,11 +4073,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4065,11 +4095,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4087,11 +4117,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4109,11 +4139,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4131,11 +4161,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4153,11 +4183,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4175,11 +4205,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4197,11 +4227,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4219,11 +4249,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4241,11 +4271,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4263,11 +4293,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4285,11 +4315,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4307,11 +4337,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4329,11 +4359,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4351,11 +4381,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4373,11 +4403,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4395,11 +4425,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4417,11 +4447,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4439,11 +4469,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4461,11 +4491,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4483,11 +4513,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4505,11 +4535,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4527,11 +4557,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4549,11 +4579,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4571,11 +4601,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4593,11 +4623,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4615,11 +4645,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4637,11 +4667,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4659,11 +4689,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4681,11 +4711,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4703,11 +4733,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4725,11 +4755,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4747,11 +4777,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4769,11 +4799,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4791,11 +4821,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4813,11 +4843,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4835,11 +4865,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4857,11 +4887,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4879,11 +4909,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4901,11 +4931,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4923,11 +4953,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -4945,11 +4975,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -4967,11 +4997,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -4989,11 +5019,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5011,11 +5041,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5033,11 +5063,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5055,11 +5085,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5077,11 +5107,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5099,11 +5129,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5121,11 +5151,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5143,11 +5173,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5165,11 +5195,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5187,11 +5217,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5209,11 +5239,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5231,11 +5261,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5253,11 +5283,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5275,11 +5305,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5297,11 +5327,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5319,11 +5349,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5341,11 +5371,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5363,11 +5393,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5385,11 +5415,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5407,11 +5437,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5429,11 +5459,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5451,11 +5481,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5473,11 +5503,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5495,11 +5525,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5517,11 +5547,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5539,11 +5569,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5561,11 +5591,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5583,11 +5613,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5605,11 +5635,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5627,11 +5657,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5649,11 +5679,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5671,11 +5701,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5693,11 +5723,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5715,11 +5745,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5737,11 +5767,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5759,11 +5789,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5781,11 +5811,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5803,11 +5833,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5825,11 +5855,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5847,11 +5877,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5869,11 +5899,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5891,11 +5921,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5913,11 +5943,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -5935,11 +5965,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -5957,11 +5987,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -5979,11 +6009,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6001,11 +6031,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6023,11 +6053,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6045,11 +6075,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6067,11 +6097,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6089,11 +6119,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6111,11 +6141,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6133,11 +6163,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6155,11 +6185,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6177,11 +6207,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6199,11 +6229,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6221,11 +6251,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6243,11 +6273,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6265,11 +6295,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6287,11 +6317,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6309,11 +6339,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6331,11 +6361,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6353,11 +6383,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6375,11 +6405,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6397,11 +6427,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6419,11 +6449,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6441,11 +6471,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6463,11 +6493,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6485,11 +6515,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6507,11 +6537,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6529,11 +6559,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6551,11 +6581,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6573,11 +6603,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6595,11 +6625,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6617,11 +6647,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6639,11 +6669,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6661,11 +6691,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6683,11 +6713,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6705,11 +6735,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6727,11 +6757,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6749,11 +6779,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6771,11 +6801,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6793,11 +6823,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6815,11 +6845,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6837,11 +6867,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6859,11 +6889,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6881,11 +6911,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6903,11 +6933,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6925,11 +6955,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -6947,11 +6977,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -6969,11 +6999,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -6991,11 +7021,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7013,11 +7043,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7035,11 +7065,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7057,11 +7087,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7079,11 +7109,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7101,11 +7131,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7123,11 +7153,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7145,11 +7175,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7167,11 +7197,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7189,11 +7219,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7211,11 +7241,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7233,11 +7263,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7255,11 +7285,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7277,11 +7307,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7299,11 +7329,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7321,11 +7351,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7343,11 +7373,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7365,11 +7395,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7387,11 +7417,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7409,11 +7439,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7431,11 +7461,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7453,11 +7483,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7475,11 +7505,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7497,11 +7527,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7519,11 +7549,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7541,11 +7571,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7563,11 +7593,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7585,11 +7615,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7607,11 +7637,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7629,11 +7659,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7651,11 +7681,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7673,11 +7703,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7695,11 +7725,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7717,11 +7747,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7739,11 +7769,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7761,11 +7791,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7783,11 +7813,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7805,11 +7835,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7827,11 +7857,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7849,11 +7879,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7871,11 +7901,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7893,11 +7923,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7915,11 +7945,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -7937,11 +7967,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -7959,11 +7989,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -7981,11 +8011,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8003,11 +8033,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8025,11 +8055,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8047,11 +8077,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8069,11 +8099,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8091,11 +8121,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8113,11 +8143,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8135,11 +8165,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8157,11 +8187,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8179,11 +8209,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8201,11 +8231,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8223,11 +8253,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8245,11 +8275,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8267,11 +8297,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8289,11 +8319,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8311,11 +8341,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8333,11 +8363,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8355,11 +8385,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8377,11 +8407,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8399,11 +8429,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8421,11 +8451,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8443,11 +8473,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8465,11 +8495,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8487,11 +8517,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8509,11 +8539,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8531,11 +8561,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8553,11 +8583,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8575,11 +8605,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8597,11 +8627,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8619,11 +8649,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8641,11 +8671,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8663,11 +8693,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8685,11 +8715,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8707,11 +8737,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8729,11 +8759,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8751,11 +8781,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8773,11 +8803,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8795,11 +8825,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8817,11 +8847,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8839,11 +8869,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8861,11 +8891,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8883,11 +8913,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8905,11 +8935,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8927,11 +8957,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -8949,11 +8979,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -8971,11 +9001,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -8993,11 +9023,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9015,11 +9045,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9037,11 +9067,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9059,11 +9089,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9081,11 +9111,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9103,11 +9133,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9125,11 +9155,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9147,11 +9177,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9169,11 +9199,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9191,11 +9221,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9213,11 +9243,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9235,11 +9265,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9257,11 +9287,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9279,11 +9309,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9301,11 +9331,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9323,11 +9353,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9345,11 +9375,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9367,11 +9397,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9389,11 +9419,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9411,11 +9441,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9433,11 +9463,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9455,11 +9485,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9477,11 +9507,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9499,11 +9529,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9521,11 +9551,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9543,11 +9573,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9565,11 +9595,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9587,11 +9617,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9609,11 +9639,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9631,11 +9661,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9653,11 +9683,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9675,11 +9705,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9697,11 +9727,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9719,11 +9749,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9741,11 +9771,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9763,11 +9793,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9785,11 +9815,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9807,11 +9837,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9829,11 +9859,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9851,11 +9881,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -9873,11 +9903,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -9895,11 +9925,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -9917,11 +9947,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -9939,11 +9969,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/Project Dataset.xlsx
+++ b/Project Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivam\OneDrive\Documents\0. MCA\Term - 1\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E95B8A1-1D64-439E-ABA1-440DCE6DB2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A48821A-D407-4DA4-9B19-3209A605E213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Was stucked on a leetcode problem for the whole day.</t>
   </si>
 </sst>
 </file>
@@ -1489,27 +1492,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B16" s="14">
+        <v>400</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>240</v>
+      </c>
+      <c r="E16" s="14">
+        <v>120</v>
+      </c>
+      <c r="F16" s="14">
+        <v>450</v>
+      </c>
+      <c r="G16" s="14">
+        <v>7</v>
+      </c>
+      <c r="H16" s="14">
+        <v>200</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" ref="I16" si="4">IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
+        <v>1440</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" ref="J16" si="5">IF(I16="","",1440-I16)</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
@@ -2687,11 +2714,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2709,11 +2736,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2731,11 +2758,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2753,11 +2780,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2775,11 +2802,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2797,11 +2824,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2819,11 +2846,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2841,11 +2868,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2863,11 +2890,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2885,11 +2912,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2907,11 +2934,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2929,11 +2956,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2951,11 +2978,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -2973,11 +3000,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -2995,11 +3022,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3017,11 +3044,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3039,11 +3066,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3061,11 +3088,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3083,11 +3110,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3105,11 +3132,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3127,11 +3154,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3149,11 +3176,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3171,11 +3198,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3193,11 +3220,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3215,11 +3242,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3237,11 +3264,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3259,11 +3286,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3281,11 +3308,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3303,11 +3330,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3325,11 +3352,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3347,11 +3374,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3369,11 +3396,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3391,11 +3418,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3413,11 +3440,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3435,11 +3462,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3457,11 +3484,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3479,11 +3506,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3501,11 +3528,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3523,11 +3550,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3545,11 +3572,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3567,11 +3594,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3589,11 +3616,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3611,11 +3638,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3633,11 +3660,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3655,11 +3682,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3677,11 +3704,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3699,11 +3726,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3721,11 +3748,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3743,11 +3770,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3765,11 +3792,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3787,11 +3814,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3809,11 +3836,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3831,11 +3858,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3853,11 +3880,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3875,11 +3902,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3897,11 +3924,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3919,11 +3946,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3941,11 +3968,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3963,11 +3990,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -3985,11 +4012,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4007,11 +4034,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4029,11 +4056,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4051,11 +4078,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4073,11 +4100,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4095,11 +4122,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4117,11 +4144,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4139,11 +4166,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4161,11 +4188,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4183,11 +4210,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4205,11 +4232,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4227,11 +4254,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4249,11 +4276,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4271,11 +4298,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4293,11 +4320,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4315,11 +4342,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4337,11 +4364,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4359,11 +4386,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4381,11 +4408,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4403,11 +4430,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4425,11 +4452,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4447,11 +4474,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4469,11 +4496,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4491,11 +4518,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4513,11 +4540,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4535,11 +4562,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4557,11 +4584,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4579,11 +4606,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4601,11 +4628,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4623,11 +4650,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4645,11 +4672,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4667,11 +4694,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4689,11 +4716,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4711,11 +4738,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4733,11 +4760,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4755,11 +4782,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4777,11 +4804,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4799,11 +4826,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4821,11 +4848,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4843,11 +4870,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4865,11 +4892,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4887,11 +4914,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4909,11 +4936,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4931,11 +4958,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4953,11 +4980,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -4975,11 +5002,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -4997,11 +5024,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5019,11 +5046,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5041,11 +5068,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5063,11 +5090,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5085,11 +5112,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5107,11 +5134,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5129,11 +5156,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5151,11 +5178,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5173,11 +5200,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5195,11 +5222,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5217,11 +5244,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5239,11 +5266,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5261,11 +5288,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5283,11 +5310,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5305,11 +5332,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5327,11 +5354,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5349,11 +5376,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5371,11 +5398,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5393,11 +5420,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5415,11 +5442,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5437,11 +5464,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5459,11 +5486,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5481,11 +5508,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5503,11 +5530,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5525,11 +5552,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5547,11 +5574,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5569,11 +5596,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5591,11 +5618,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5613,11 +5640,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5635,11 +5662,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5657,11 +5684,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5679,11 +5706,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5701,11 +5728,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5723,11 +5750,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5745,11 +5772,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5767,11 +5794,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5789,11 +5816,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5811,11 +5838,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5833,11 +5860,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5855,11 +5882,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5877,11 +5904,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5899,11 +5926,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5921,11 +5948,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5943,11 +5970,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -5965,11 +5992,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -5987,11 +6014,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6009,11 +6036,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6031,11 +6058,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6053,11 +6080,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6075,11 +6102,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6097,11 +6124,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6119,11 +6146,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6141,11 +6168,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6163,11 +6190,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6185,11 +6212,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6207,11 +6234,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6229,11 +6256,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6251,11 +6278,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6273,11 +6300,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6295,11 +6322,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6317,11 +6344,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6339,11 +6366,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6361,11 +6388,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6383,11 +6410,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6405,11 +6432,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6427,11 +6454,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6449,11 +6476,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6471,11 +6498,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6493,11 +6520,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6515,11 +6542,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6537,11 +6564,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6559,11 +6586,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6581,11 +6608,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6603,11 +6630,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6625,11 +6652,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6647,11 +6674,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6669,11 +6696,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6691,11 +6718,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6713,11 +6740,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6735,11 +6762,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6757,11 +6784,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6779,11 +6806,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6801,11 +6828,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6823,11 +6850,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6845,11 +6872,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6867,11 +6894,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6889,11 +6916,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6911,11 +6938,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6933,11 +6960,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6955,11 +6982,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -6977,11 +7004,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -6999,11 +7026,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7021,11 +7048,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7043,11 +7070,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7065,11 +7092,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7087,11 +7114,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7109,11 +7136,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7131,11 +7158,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7153,11 +7180,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7175,11 +7202,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7197,11 +7224,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7219,11 +7246,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7241,11 +7268,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7263,11 +7290,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7285,11 +7312,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7307,11 +7334,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7329,11 +7356,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7351,11 +7378,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7373,11 +7400,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7395,11 +7422,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7417,11 +7444,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7439,11 +7466,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7461,11 +7488,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7483,11 +7510,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7505,11 +7532,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7527,11 +7554,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7549,11 +7576,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7571,11 +7598,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7593,11 +7620,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7615,11 +7642,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7637,11 +7664,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7659,11 +7686,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7681,11 +7708,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7703,11 +7730,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7725,11 +7752,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7747,11 +7774,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7769,11 +7796,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7791,11 +7818,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7813,11 +7840,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7835,11 +7862,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7857,11 +7884,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7879,11 +7906,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7901,11 +7928,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7923,11 +7950,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7945,11 +7972,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -7967,11 +7994,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -7989,11 +8016,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8011,11 +8038,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8033,11 +8060,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8055,11 +8082,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8077,11 +8104,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8099,11 +8126,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8121,11 +8148,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8143,11 +8170,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8165,11 +8192,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8187,11 +8214,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8209,11 +8236,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8231,11 +8258,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8253,11 +8280,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8275,11 +8302,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8297,11 +8324,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8319,11 +8346,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8341,11 +8368,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8363,11 +8390,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8385,11 +8412,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8407,11 +8434,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8429,11 +8456,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8451,11 +8478,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8473,11 +8500,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8495,11 +8522,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8517,11 +8544,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8539,11 +8566,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8561,11 +8588,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8583,11 +8610,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8605,11 +8632,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8627,11 +8654,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8649,11 +8676,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8671,11 +8698,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8693,11 +8720,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8715,11 +8742,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8737,11 +8764,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8759,11 +8786,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8781,11 +8808,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8803,11 +8830,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8825,11 +8852,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8847,11 +8874,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8869,11 +8896,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8891,11 +8918,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8913,11 +8940,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8935,11 +8962,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8957,11 +8984,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -8979,11 +9006,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9001,11 +9028,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9023,11 +9050,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9045,11 +9072,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9067,11 +9094,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9089,11 +9116,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9111,11 +9138,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9133,11 +9160,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9155,11 +9182,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9177,11 +9204,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9199,11 +9226,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9221,11 +9248,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9243,11 +9270,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9265,11 +9292,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9287,11 +9314,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9309,11 +9336,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9331,11 +9358,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9353,11 +9380,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9375,11 +9402,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9397,11 +9424,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9419,11 +9446,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9441,11 +9468,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9463,11 +9490,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9485,11 +9512,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9507,11 +9534,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9529,11 +9556,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9551,11 +9578,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9573,11 +9600,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9595,11 +9622,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9617,11 +9644,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9639,11 +9666,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9661,11 +9688,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9683,11 +9710,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9705,11 +9732,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9727,11 +9754,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9749,11 +9776,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9771,11 +9798,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9793,11 +9820,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9815,11 +9842,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9837,11 +9864,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9859,11 +9886,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9881,11 +9908,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -9903,11 +9930,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -9925,11 +9952,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -9947,11 +9974,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -9969,11 +9996,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/Project Dataset.xlsx
+++ b/Project Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivam\OneDrive\Documents\0. MCA\Term - 1\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A48821A-D407-4DA4-9B19-3209A605E213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24768719-6F69-4A7E-B9F5-16399BFA3540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>Was stucked on a leetcode problem for the whole day.</t>
+  </si>
+  <si>
+    <t>Weekends are on.</t>
   </si>
 </sst>
 </file>
@@ -1539,26 +1542,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="A17" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B17" s="14">
+        <v>600</v>
+      </c>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14">
+        <v>370</v>
+      </c>
+      <c r="E17" s="14">
+        <v>120</v>
+      </c>
+      <c r="F17" s="14">
+        <v>120</v>
+      </c>
+      <c r="G17" s="14">
+        <v>2</v>
+      </c>
+      <c r="H17" s="14">
+        <v>200</v>
+      </c>
+      <c r="I17" s="15">
+        <f t="shared" ref="I17" si="6">IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
+        <v>1440</v>
+      </c>
+      <c r="J17" s="15">
+        <f t="shared" ref="J17" si="7">IF(I17="","",1440-I17)</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
@@ -2714,11 +2741,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="8">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="9">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2736,11 +2763,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2758,11 +2785,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2780,11 +2807,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2802,11 +2829,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2824,11 +2851,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2846,11 +2873,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2868,11 +2895,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2890,11 +2917,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2912,11 +2939,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2934,11 +2961,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2956,11 +2983,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2978,11 +3005,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3000,11 +3027,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3022,11 +3049,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3044,11 +3071,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3066,11 +3093,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3088,11 +3115,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3110,11 +3137,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3132,11 +3159,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3154,11 +3181,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3176,11 +3203,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3198,11 +3225,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3220,11 +3247,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3242,11 +3269,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3264,11 +3291,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3286,11 +3313,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3308,11 +3335,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3330,11 +3357,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3352,11 +3379,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3374,11 +3401,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3396,11 +3423,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3418,11 +3445,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3440,11 +3467,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3462,11 +3489,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3484,11 +3511,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3506,11 +3533,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3528,11 +3555,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3550,11 +3577,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3572,11 +3599,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3594,11 +3621,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3616,11 +3643,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3638,11 +3665,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3660,11 +3687,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3682,11 +3709,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3704,11 +3731,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3726,11 +3753,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3748,11 +3775,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3770,11 +3797,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3792,11 +3819,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3814,11 +3841,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3836,11 +3863,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3858,11 +3885,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3880,11 +3907,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3902,11 +3929,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3924,11 +3951,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3946,11 +3973,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3968,11 +3995,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3990,11 +4017,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4012,11 +4039,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4034,11 +4061,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4056,11 +4083,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4078,11 +4105,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4100,11 +4127,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4122,11 +4149,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="10">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="11">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4144,11 +4171,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4166,11 +4193,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4188,11 +4215,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4210,11 +4237,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4232,11 +4259,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4254,11 +4281,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4276,11 +4303,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4298,11 +4325,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4320,11 +4347,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4342,11 +4369,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4364,11 +4391,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4386,11 +4413,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4408,11 +4435,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4430,11 +4457,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4452,11 +4479,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4474,11 +4501,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4496,11 +4523,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4518,11 +4545,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4540,11 +4567,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4562,11 +4589,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4584,11 +4611,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4606,11 +4633,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4628,11 +4655,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4650,11 +4677,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4672,11 +4699,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4694,11 +4721,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4716,11 +4743,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4738,11 +4765,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4760,11 +4787,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4782,11 +4809,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4804,11 +4831,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4826,11 +4853,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4848,11 +4875,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4870,11 +4897,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4892,11 +4919,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4914,11 +4941,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4936,11 +4963,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4958,11 +4985,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4980,11 +5007,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5002,11 +5029,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5024,11 +5051,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5046,11 +5073,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5068,11 +5095,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5090,11 +5117,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5112,11 +5139,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5134,11 +5161,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5156,11 +5183,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5178,11 +5205,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5200,11 +5227,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5222,11 +5249,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5244,11 +5271,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5266,11 +5293,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5288,11 +5315,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5310,11 +5337,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5332,11 +5359,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5354,11 +5381,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5376,11 +5403,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5398,11 +5425,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5420,11 +5447,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5442,11 +5469,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5464,11 +5491,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5486,11 +5513,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5508,11 +5535,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5530,11 +5557,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="12">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="13">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5552,11 +5579,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5574,11 +5601,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5596,11 +5623,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5618,11 +5645,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5640,11 +5667,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5662,11 +5689,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5684,11 +5711,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5706,11 +5733,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5728,11 +5755,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5750,11 +5777,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5772,11 +5799,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5794,11 +5821,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5816,11 +5843,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5838,11 +5865,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5860,11 +5887,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5882,11 +5909,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5904,11 +5931,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5926,11 +5953,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5948,11 +5975,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5970,11 +5997,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -5992,11 +6019,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6014,11 +6041,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6036,11 +6063,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6058,11 +6085,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6080,11 +6107,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6102,11 +6129,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6124,11 +6151,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6146,11 +6173,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6168,11 +6195,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6190,11 +6217,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6212,11 +6239,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6234,11 +6261,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6256,11 +6283,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6278,11 +6305,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6300,11 +6327,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6322,11 +6349,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6344,11 +6371,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6366,11 +6393,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6388,11 +6415,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6410,11 +6437,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6432,11 +6459,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6454,11 +6481,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6476,11 +6503,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6498,11 +6525,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6520,11 +6547,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6542,11 +6569,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6564,11 +6591,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6586,11 +6613,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6608,11 +6635,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6630,11 +6657,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6652,11 +6679,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6674,11 +6701,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6696,11 +6723,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6718,11 +6745,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6740,11 +6767,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6762,11 +6789,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6784,11 +6811,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6806,11 +6833,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6828,11 +6855,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6850,11 +6877,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6872,11 +6899,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6894,11 +6921,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6916,11 +6943,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6938,11 +6965,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="14">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="15">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6960,11 +6987,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6982,11 +7009,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7004,11 +7031,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7026,11 +7053,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7048,11 +7075,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7070,11 +7097,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7092,11 +7119,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7114,11 +7141,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7136,11 +7163,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7158,11 +7185,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7180,11 +7207,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7202,11 +7229,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7224,11 +7251,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7246,11 +7273,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7268,11 +7295,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7290,11 +7317,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7312,11 +7339,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7334,11 +7361,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7356,11 +7383,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7378,11 +7405,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7400,11 +7427,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7422,11 +7449,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7444,11 +7471,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7466,11 +7493,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7488,11 +7515,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7510,11 +7537,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7532,11 +7559,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7554,11 +7581,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7576,11 +7603,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7598,11 +7625,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7620,11 +7647,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7642,11 +7669,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7664,11 +7691,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7686,11 +7713,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7708,11 +7735,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7730,11 +7757,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7752,11 +7779,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7774,11 +7801,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7796,11 +7823,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7818,11 +7845,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7840,11 +7867,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7862,11 +7889,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7884,11 +7911,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7906,11 +7933,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7928,11 +7955,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7950,11 +7977,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7972,11 +7999,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -7994,11 +8021,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8016,11 +8043,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8038,11 +8065,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8060,11 +8087,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8082,11 +8109,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8104,11 +8131,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8126,11 +8153,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8148,11 +8175,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8170,11 +8197,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8192,11 +8219,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8214,11 +8241,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8236,11 +8263,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8258,11 +8285,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8280,11 +8307,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8302,11 +8329,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8324,11 +8351,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8346,11 +8373,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="16">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="17">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8368,11 +8395,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8390,11 +8417,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8412,11 +8439,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8434,11 +8461,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8456,11 +8483,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8478,11 +8505,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8500,11 +8527,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8522,11 +8549,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8544,11 +8571,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8566,11 +8593,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8588,11 +8615,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8610,11 +8637,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8632,11 +8659,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8654,11 +8681,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8676,11 +8703,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8698,11 +8725,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8720,11 +8747,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8742,11 +8769,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8764,11 +8791,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8786,11 +8813,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8808,11 +8835,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8830,11 +8857,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8852,11 +8879,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8874,11 +8901,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8896,11 +8923,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8918,11 +8945,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8940,11 +8967,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8962,11 +8989,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8984,11 +9011,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9006,11 +9033,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9028,11 +9055,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9050,11 +9077,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9072,11 +9099,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9094,11 +9121,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9116,11 +9143,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9138,11 +9165,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9160,11 +9187,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9182,11 +9209,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9204,11 +9231,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9226,11 +9253,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9248,11 +9275,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9270,11 +9297,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9292,11 +9319,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9314,11 +9341,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9336,11 +9363,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9358,11 +9385,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9380,11 +9407,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9402,11 +9429,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9424,11 +9451,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9446,11 +9473,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9468,11 +9495,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9490,11 +9517,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9512,11 +9539,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9534,11 +9561,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9556,11 +9583,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9578,11 +9605,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9600,11 +9627,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9622,11 +9649,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9644,11 +9671,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9666,11 +9693,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9688,11 +9715,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9710,11 +9737,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9732,11 +9759,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9754,11 +9781,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="18">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="19">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9776,11 +9803,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9798,11 +9825,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9820,11 +9847,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9842,11 +9869,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9864,11 +9891,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9886,11 +9913,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9908,11 +9935,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -9930,11 +9957,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -9952,11 +9979,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -9974,11 +10001,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -9996,11 +10023,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/Project Dataset.xlsx
+++ b/Project Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivam\OneDrive\Documents\0. MCA\Term - 1\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24768719-6F69-4A7E-B9F5-16399BFA3540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AC813B-A22A-460D-9130-0A56B51EEA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,12 @@
   </si>
   <si>
     <t>Weekends are on.</t>
+  </si>
+  <si>
+    <t>Solved the question which was pending for a while.</t>
+  </si>
+  <si>
+    <t>Very busy Sunday.</t>
   </si>
 </sst>
 </file>
@@ -1587,49 +1593,97 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B18" s="14">
+        <v>600</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>300</v>
+      </c>
+      <c r="E18" s="14">
+        <v>180</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>330</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" ref="I18:I19" si="8">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
+        <v>1440</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" ref="J18:J19" si="9">IF(I18="","",1440-I18)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+      <c r="A19" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B19" s="14">
+        <v>600</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>360</v>
+      </c>
+      <c r="E19" s="14">
+        <v>180</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>270</v>
+      </c>
+      <c r="I19" s="15">
+        <f t="shared" si="8"/>
+        <v>1440</v>
+      </c>
+      <c r="J19" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
@@ -2741,11 +2795,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="8">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="10">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="9">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="11">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2763,11 +2817,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2785,11 +2839,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2807,11 +2861,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2829,11 +2883,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2851,11 +2905,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2873,11 +2927,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2895,11 +2949,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2917,11 +2971,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2939,11 +2993,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2961,11 +3015,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2983,11 +3037,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3005,11 +3059,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3027,11 +3081,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3049,11 +3103,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3071,11 +3125,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3093,11 +3147,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3115,11 +3169,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3137,11 +3191,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3159,11 +3213,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3181,11 +3235,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3203,11 +3257,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3225,11 +3279,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3247,11 +3301,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3269,11 +3323,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3291,11 +3345,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3313,11 +3367,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3335,11 +3389,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3357,11 +3411,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3379,11 +3433,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3401,11 +3455,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3423,11 +3477,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3445,11 +3499,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3467,11 +3521,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3489,11 +3543,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3511,11 +3565,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3533,11 +3587,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3555,11 +3609,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3577,11 +3631,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3599,11 +3653,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3621,11 +3675,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3643,11 +3697,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3665,11 +3719,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3687,11 +3741,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3709,11 +3763,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3731,11 +3785,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3753,11 +3807,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3775,11 +3829,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3797,11 +3851,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3819,11 +3873,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3841,11 +3895,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3863,11 +3917,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3885,11 +3939,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3907,11 +3961,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3929,11 +3983,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3951,11 +4005,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3973,11 +4027,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3995,11 +4049,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4017,11 +4071,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4039,11 +4093,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4061,11 +4115,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4083,11 +4137,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4105,11 +4159,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4127,11 +4181,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4149,11 +4203,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="10">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="12">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="11">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="13">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4171,11 +4225,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4193,11 +4247,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4215,11 +4269,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4237,11 +4291,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4259,11 +4313,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4281,11 +4335,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4303,11 +4357,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4325,11 +4379,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4347,11 +4401,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4369,11 +4423,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4391,11 +4445,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4413,11 +4467,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4435,11 +4489,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4457,11 +4511,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4479,11 +4533,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4501,11 +4555,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4523,11 +4577,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4545,11 +4599,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4567,11 +4621,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4589,11 +4643,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4611,11 +4665,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4633,11 +4687,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4655,11 +4709,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4677,11 +4731,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4699,11 +4753,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4721,11 +4775,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4743,11 +4797,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4765,11 +4819,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4787,11 +4841,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4809,11 +4863,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4831,11 +4885,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4853,11 +4907,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4875,11 +4929,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4897,11 +4951,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4919,11 +4973,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4941,11 +4995,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4963,11 +5017,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4985,11 +5039,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5007,11 +5061,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5029,11 +5083,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5051,11 +5105,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5073,11 +5127,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5095,11 +5149,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5117,11 +5171,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5139,11 +5193,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5161,11 +5215,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5183,11 +5237,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5205,11 +5259,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5227,11 +5281,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5249,11 +5303,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5271,11 +5325,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5293,11 +5347,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5315,11 +5369,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5337,11 +5391,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5359,11 +5413,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5381,11 +5435,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5403,11 +5457,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5425,11 +5479,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5447,11 +5501,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5469,11 +5523,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5491,11 +5545,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5513,11 +5567,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5535,11 +5589,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5557,11 +5611,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="12">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="14">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="13">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="15">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5579,11 +5633,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5601,11 +5655,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5623,11 +5677,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5645,11 +5699,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5667,11 +5721,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5689,11 +5743,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5711,11 +5765,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5733,11 +5787,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5755,11 +5809,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5777,11 +5831,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5799,11 +5853,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5821,11 +5875,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5843,11 +5897,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5865,11 +5919,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5887,11 +5941,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5909,11 +5963,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5931,11 +5985,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5953,11 +6007,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5975,11 +6029,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5997,11 +6051,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6019,11 +6073,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6041,11 +6095,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6063,11 +6117,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6085,11 +6139,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6107,11 +6161,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6129,11 +6183,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6151,11 +6205,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6173,11 +6227,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6195,11 +6249,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6217,11 +6271,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6239,11 +6293,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6261,11 +6315,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6283,11 +6337,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6305,11 +6359,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6327,11 +6381,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6349,11 +6403,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6371,11 +6425,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6393,11 +6447,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6415,11 +6469,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6437,11 +6491,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6459,11 +6513,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6481,11 +6535,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6503,11 +6557,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6525,11 +6579,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6547,11 +6601,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6569,11 +6623,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6591,11 +6645,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6613,11 +6667,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6635,11 +6689,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6657,11 +6711,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6679,11 +6733,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6701,11 +6755,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6723,11 +6777,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6745,11 +6799,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6767,11 +6821,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6789,11 +6843,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6811,11 +6865,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6833,11 +6887,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6855,11 +6909,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6877,11 +6931,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6899,11 +6953,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6921,11 +6975,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6943,11 +6997,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6965,11 +7019,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="14">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="16">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="15">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="17">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6987,11 +7041,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7009,11 +7063,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7031,11 +7085,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7053,11 +7107,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7075,11 +7129,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7097,11 +7151,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7119,11 +7173,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7141,11 +7195,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7163,11 +7217,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7185,11 +7239,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7207,11 +7261,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7229,11 +7283,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7251,11 +7305,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7273,11 +7327,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7295,11 +7349,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7317,11 +7371,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7339,11 +7393,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7361,11 +7415,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7383,11 +7437,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7405,11 +7459,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7427,11 +7481,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7449,11 +7503,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7471,11 +7525,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7493,11 +7547,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7515,11 +7569,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7537,11 +7591,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7559,11 +7613,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7581,11 +7635,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7603,11 +7657,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7625,11 +7679,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7647,11 +7701,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7669,11 +7723,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7691,11 +7745,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7713,11 +7767,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7735,11 +7789,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7757,11 +7811,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7779,11 +7833,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7801,11 +7855,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7823,11 +7877,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7845,11 +7899,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7867,11 +7921,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7889,11 +7943,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7911,11 +7965,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7933,11 +7987,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7955,11 +8009,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7977,11 +8031,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7999,11 +8053,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8021,11 +8075,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8043,11 +8097,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8065,11 +8119,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8087,11 +8141,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8109,11 +8163,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8131,11 +8185,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8153,11 +8207,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8175,11 +8229,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8197,11 +8251,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8219,11 +8273,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8241,11 +8295,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8263,11 +8317,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8285,11 +8339,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8307,11 +8361,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8329,11 +8383,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8351,11 +8405,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8373,11 +8427,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="16">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="18">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="17">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="19">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8395,11 +8449,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8417,11 +8471,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8439,11 +8493,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8461,11 +8515,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8483,11 +8537,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8505,11 +8559,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8527,11 +8581,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8549,11 +8603,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8571,11 +8625,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8593,11 +8647,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8615,11 +8669,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8637,11 +8691,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8659,11 +8713,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8681,11 +8735,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8703,11 +8757,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8725,11 +8779,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8747,11 +8801,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8769,11 +8823,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8791,11 +8845,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8813,11 +8867,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8835,11 +8889,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8857,11 +8911,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8879,11 +8933,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8901,11 +8955,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8923,11 +8977,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8945,11 +8999,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8967,11 +9021,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8989,11 +9043,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9011,11 +9065,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9033,11 +9087,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9055,11 +9109,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9077,11 +9131,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9099,11 +9153,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9121,11 +9175,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9143,11 +9197,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9165,11 +9219,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9187,11 +9241,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9209,11 +9263,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9231,11 +9285,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9253,11 +9307,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9275,11 +9329,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9297,11 +9351,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9319,11 +9373,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9341,11 +9395,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9363,11 +9417,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9385,11 +9439,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9407,11 +9461,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9429,11 +9483,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9451,11 +9505,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9473,11 +9527,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9495,11 +9549,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9517,11 +9571,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9539,11 +9593,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9561,11 +9615,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9583,11 +9637,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9605,11 +9659,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9627,11 +9681,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9649,11 +9703,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9671,11 +9725,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9693,11 +9747,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9715,11 +9769,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9737,11 +9791,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9759,11 +9813,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9781,11 +9835,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="18">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="20">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="19">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="21">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9803,11 +9857,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9825,11 +9879,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9847,11 +9901,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9869,11 +9923,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9891,11 +9945,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9913,11 +9967,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9935,11 +9989,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -9957,11 +10011,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -9979,11 +10033,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10001,11 +10055,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10023,11 +10077,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/Project Dataset.xlsx
+++ b/Project Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivam\OneDrive\Documents\0. MCA\Term - 1\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AC813B-A22A-460D-9130-0A56B51EEA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E6A94F5-69B3-4DEC-9564-1FE00BD16862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1686,26 +1686,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+      <c r="A20" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B20" s="14">
+        <v>300</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>480</v>
+      </c>
+      <c r="E20" s="14">
+        <v>180</v>
+      </c>
+      <c r="F20" s="14">
+        <v>200</v>
+      </c>
+      <c r="G20" s="14">
+        <v>3</v>
+      </c>
+      <c r="H20" s="14">
+        <v>250</v>
+      </c>
+      <c r="I20" s="15">
+        <f t="shared" ref="I20" si="10">IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
+        <v>1440</v>
+      </c>
+      <c r="J20" s="15">
+        <f t="shared" ref="J20" si="11">IF(I20="","",1440-I20)</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
@@ -2795,11 +2819,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="10">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="12">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="11">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="13">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2817,11 +2841,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2839,11 +2863,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2861,11 +2885,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2883,11 +2907,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2905,11 +2929,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2927,11 +2951,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2949,11 +2973,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2971,11 +2995,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2993,11 +3017,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3015,11 +3039,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3037,11 +3061,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3059,11 +3083,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3081,11 +3105,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3103,11 +3127,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3125,11 +3149,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3147,11 +3171,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3169,11 +3193,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3191,11 +3215,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3213,11 +3237,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3235,11 +3259,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3257,11 +3281,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3279,11 +3303,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3301,11 +3325,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3323,11 +3347,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3345,11 +3369,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3367,11 +3391,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3389,11 +3413,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3411,11 +3435,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3433,11 +3457,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3455,11 +3479,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3477,11 +3501,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3499,11 +3523,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3521,11 +3545,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3543,11 +3567,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3565,11 +3589,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3587,11 +3611,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3609,11 +3633,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3631,11 +3655,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3653,11 +3677,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3675,11 +3699,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3697,11 +3721,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3719,11 +3743,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3741,11 +3765,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3763,11 +3787,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3785,11 +3809,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3807,11 +3831,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3829,11 +3853,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3851,11 +3875,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3873,11 +3897,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3895,11 +3919,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3917,11 +3941,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3939,11 +3963,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3961,11 +3985,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3983,11 +4007,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4005,11 +4029,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4027,11 +4051,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4049,11 +4073,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4071,11 +4095,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4093,11 +4117,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4115,11 +4139,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4137,11 +4161,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4159,11 +4183,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4181,11 +4205,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4203,11 +4227,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="12">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="14">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="13">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="15">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4225,11 +4249,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4247,11 +4271,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4269,11 +4293,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4291,11 +4315,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4313,11 +4337,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4335,11 +4359,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4357,11 +4381,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4379,11 +4403,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4401,11 +4425,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4423,11 +4447,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4445,11 +4469,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4467,11 +4491,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4489,11 +4513,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4511,11 +4535,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4533,11 +4557,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4555,11 +4579,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4577,11 +4601,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4599,11 +4623,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4621,11 +4645,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4643,11 +4667,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4665,11 +4689,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4687,11 +4711,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4709,11 +4733,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4731,11 +4755,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4753,11 +4777,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4775,11 +4799,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4797,11 +4821,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4819,11 +4843,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4841,11 +4865,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4863,11 +4887,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4885,11 +4909,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4907,11 +4931,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4929,11 +4953,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4951,11 +4975,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4973,11 +4997,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4995,11 +5019,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5017,11 +5041,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5039,11 +5063,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5061,11 +5085,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5083,11 +5107,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5105,11 +5129,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5127,11 +5151,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5149,11 +5173,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5171,11 +5195,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5193,11 +5217,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5215,11 +5239,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5237,11 +5261,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5259,11 +5283,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5281,11 +5305,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5303,11 +5327,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5325,11 +5349,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5347,11 +5371,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5369,11 +5393,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5391,11 +5415,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5413,11 +5437,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5435,11 +5459,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5457,11 +5481,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5479,11 +5503,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5501,11 +5525,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5523,11 +5547,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5545,11 +5569,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5567,11 +5591,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5589,11 +5613,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5611,11 +5635,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="14">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="16">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="15">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="17">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5633,11 +5657,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5655,11 +5679,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5677,11 +5701,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5699,11 +5723,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5721,11 +5745,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5743,11 +5767,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5765,11 +5789,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5787,11 +5811,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5809,11 +5833,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5831,11 +5855,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5853,11 +5877,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5875,11 +5899,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5897,11 +5921,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5919,11 +5943,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5941,11 +5965,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5963,11 +5987,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5985,11 +6009,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6007,11 +6031,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6029,11 +6053,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6051,11 +6075,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6073,11 +6097,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6095,11 +6119,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6117,11 +6141,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6139,11 +6163,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6161,11 +6185,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6183,11 +6207,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6205,11 +6229,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6227,11 +6251,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6249,11 +6273,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6271,11 +6295,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6293,11 +6317,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6315,11 +6339,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6337,11 +6361,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6359,11 +6383,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6381,11 +6405,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6403,11 +6427,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6425,11 +6449,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6447,11 +6471,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6469,11 +6493,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6491,11 +6515,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6513,11 +6537,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6535,11 +6559,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6557,11 +6581,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6579,11 +6603,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6601,11 +6625,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6623,11 +6647,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6645,11 +6669,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6667,11 +6691,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6689,11 +6713,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6711,11 +6735,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6733,11 +6757,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6755,11 +6779,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6777,11 +6801,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6799,11 +6823,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6821,11 +6845,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6843,11 +6867,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6865,11 +6889,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6887,11 +6911,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6909,11 +6933,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6931,11 +6955,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6953,11 +6977,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6975,11 +6999,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6997,11 +7021,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7019,11 +7043,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="16">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="18">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="17">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="19">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7041,11 +7065,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7063,11 +7087,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7085,11 +7109,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7107,11 +7131,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7129,11 +7153,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7151,11 +7175,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7173,11 +7197,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7195,11 +7219,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7217,11 +7241,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7239,11 +7263,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7261,11 +7285,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7283,11 +7307,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7305,11 +7329,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7327,11 +7351,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7349,11 +7373,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7371,11 +7395,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7393,11 +7417,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7415,11 +7439,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7437,11 +7461,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7459,11 +7483,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7481,11 +7505,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7503,11 +7527,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7525,11 +7549,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7547,11 +7571,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7569,11 +7593,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7591,11 +7615,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7613,11 +7637,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7635,11 +7659,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7657,11 +7681,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7679,11 +7703,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7701,11 +7725,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7723,11 +7747,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7745,11 +7769,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7767,11 +7791,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7789,11 +7813,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7811,11 +7835,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7833,11 +7857,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7855,11 +7879,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7877,11 +7901,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7899,11 +7923,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7921,11 +7945,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7943,11 +7967,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7965,11 +7989,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7987,11 +8011,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8009,11 +8033,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8031,11 +8055,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8053,11 +8077,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8075,11 +8099,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8097,11 +8121,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8119,11 +8143,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8141,11 +8165,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8163,11 +8187,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8185,11 +8209,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8207,11 +8231,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8229,11 +8253,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8251,11 +8275,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8273,11 +8297,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8295,11 +8319,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8317,11 +8341,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8339,11 +8363,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8361,11 +8385,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8383,11 +8407,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8405,11 +8429,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8427,11 +8451,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="18">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="20">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="19">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="21">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8449,11 +8473,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8471,11 +8495,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8493,11 +8517,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8515,11 +8539,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8537,11 +8561,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8559,11 +8583,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8581,11 +8605,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8603,11 +8627,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8625,11 +8649,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8647,11 +8671,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8669,11 +8693,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8691,11 +8715,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8713,11 +8737,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8735,11 +8759,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8757,11 +8781,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8779,11 +8803,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8801,11 +8825,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8823,11 +8847,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8845,11 +8869,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8867,11 +8891,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8889,11 +8913,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8911,11 +8935,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8933,11 +8957,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8955,11 +8979,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8977,11 +9001,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8999,11 +9023,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9021,11 +9045,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9043,11 +9067,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9065,11 +9089,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9087,11 +9111,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9109,11 +9133,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9131,11 +9155,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9153,11 +9177,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9175,11 +9199,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9197,11 +9221,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9219,11 +9243,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9241,11 +9265,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9263,11 +9287,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9285,11 +9309,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9307,11 +9331,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9329,11 +9353,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9351,11 +9375,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9373,11 +9397,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9395,11 +9419,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9417,11 +9441,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9439,11 +9463,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9461,11 +9485,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9483,11 +9507,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9505,11 +9529,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9527,11 +9551,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9549,11 +9573,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9571,11 +9595,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9593,11 +9617,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9615,11 +9639,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9637,11 +9661,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9659,11 +9683,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9681,11 +9705,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9703,11 +9727,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9725,11 +9749,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9747,11 +9771,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9769,11 +9793,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9791,11 +9815,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9813,11 +9837,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9835,11 +9859,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="20">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="22">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="21">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="23">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9857,11 +9881,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9879,11 +9903,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9901,11 +9925,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9923,11 +9947,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9945,11 +9969,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9967,11 +9991,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9989,11 +10013,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10011,11 +10035,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10033,11 +10057,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10055,11 +10079,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10077,11 +10101,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/Project Dataset.xlsx
+++ b/Project Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivam\OneDrive\Documents\0. MCA\Term - 1\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E6A94F5-69B3-4DEC-9564-1FE00BD16862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93F9788-FDFB-45F2-A2EE-70C189DD5831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -205,9 +205,6 @@
     <t>CAP-776</t>
   </si>
   <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>Neutral</t>
   </si>
   <si>
@@ -263,6 +260,39 @@
   </si>
   <si>
     <t>Very busy Sunday.</t>
+  </si>
+  <si>
+    <t>Started working on a new project idea.</t>
+  </si>
+  <si>
+    <t>Got late while returning back home.</t>
+  </si>
+  <si>
+    <t>Had a CA but didn't get chance as time was up.</t>
+  </si>
+  <si>
+    <t>Boring Day.</t>
+  </si>
+  <si>
+    <t>Nothing special other than the weekends.</t>
+  </si>
+  <si>
+    <t>Solved a good set of problems on leetcode.</t>
+  </si>
+  <si>
+    <t>Wasn't able to participate in SIH bcoz slots were full.</t>
+  </si>
+  <si>
+    <t>Had a CA n it went good imo.</t>
+  </si>
+  <si>
+    <t>Maintained my streak on leetcode.</t>
+  </si>
+  <si>
+    <t>Met an old friend.</t>
+  </si>
+  <si>
+    <t>Sepetember</t>
   </si>
 </sst>
 </file>
@@ -975,7 +1005,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1121,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>50</v>
@@ -1130,7 +1160,7 @@
         <v>51</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1173,10 +1203,10 @@
         <v>50</v>
       </c>
       <c r="M8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1222,7 +1252,7 @@
         <v>51</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1265,10 +1295,10 @@
         <v>50</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1305,16 +1335,16 @@
         <v>0</v>
       </c>
       <c r="K11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11" s="16" t="s">
         <v>63</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>64</v>
       </c>
       <c r="M11" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1354,13 +1384,13 @@
         <v>49</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1397,16 +1427,16 @@
         <v>0</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L13" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1449,10 +1479,10 @@
         <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N14" s="17" t="s">
         <v>68</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1489,16 +1519,16 @@
         <v>0</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1535,16 +1565,16 @@
         <v>0</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1581,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="K17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L17" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="L17" s="16" t="s">
-        <v>64</v>
-      </c>
       <c r="M17" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1627,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L18" s="16" t="s">
         <v>50</v>
@@ -1636,7 +1666,7 @@
         <v>51</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1673,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
         <v>46265</v>
       </c>
@@ -1719,215 +1749,431 @@
         <v>0</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="14">
+        <v>360</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>300</v>
+      </c>
+      <c r="E21" s="14">
+        <v>120</v>
+      </c>
+      <c r="F21" s="14">
+        <v>450</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>180</v>
+      </c>
+      <c r="I21" s="15">
+        <f t="shared" ref="I21:I31" si="12">IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
+        <v>1440</v>
+      </c>
+      <c r="J21" s="15">
+        <f t="shared" ref="J21:J31" si="13">IF(I21="","",1440-I21)</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="14">
+        <v>500</v>
+      </c>
+      <c r="C22" s="14">
+        <v>30</v>
+      </c>
+      <c r="D22" s="14">
+        <v>300</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>190</v>
+      </c>
+      <c r="I22" s="15">
+        <f t="shared" si="12"/>
+        <v>1440</v>
+      </c>
+      <c r="J22" s="15">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+      <c r="A23" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="14">
+        <v>300</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>300</v>
+      </c>
+      <c r="E23" s="14">
+        <v>180</v>
+      </c>
+      <c r="F23" s="14">
+        <v>450</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>180</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" si="12"/>
+        <v>1440</v>
+      </c>
+      <c r="J23" s="15">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="14">
+        <v>400</v>
+      </c>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>300</v>
+      </c>
+      <c r="E24" s="14">
+        <v>120</v>
+      </c>
+      <c r="F24" s="14">
+        <v>360</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>230</v>
+      </c>
+      <c r="I24" s="15">
+        <f t="shared" si="12"/>
+        <v>1440</v>
+      </c>
+      <c r="J24" s="15">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="14">
+        <v>600</v>
+      </c>
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
+        <v>300</v>
+      </c>
+      <c r="E25" s="14">
+        <v>180</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>330</v>
+      </c>
+      <c r="I25" s="15">
+        <f t="shared" si="12"/>
+        <v>1440</v>
+      </c>
+      <c r="J25" s="15">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="14">
+        <v>600</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>360</v>
+      </c>
+      <c r="E26" s="14">
+        <v>180</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>270</v>
+      </c>
+      <c r="I26" s="15">
+        <f t="shared" si="12"/>
+        <v>1440</v>
+      </c>
+      <c r="J26" s="15">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+      <c r="A27" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="14">
+        <v>300</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>320</v>
+      </c>
+      <c r="E27" s="14">
+        <v>180</v>
+      </c>
+      <c r="F27" s="14">
+        <v>360</v>
+      </c>
+      <c r="G27" s="14">
+        <v>3</v>
+      </c>
+      <c r="H27" s="14">
+        <v>250</v>
+      </c>
+      <c r="I27" s="15">
+        <f t="shared" si="12"/>
+        <v>1440</v>
+      </c>
+      <c r="J27" s="15">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B28" s="14">
+        <v>300</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>360</v>
+      </c>
+      <c r="E28" s="14">
+        <v>180</v>
+      </c>
+      <c r="F28" s="14">
+        <v>450</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>120</v>
+      </c>
+      <c r="I28" s="15">
+        <f t="shared" si="12"/>
+        <v>1440</v>
+      </c>
+      <c r="J28" s="15">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+      <c r="A29" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="14">
+        <v>360</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>400</v>
+      </c>
+      <c r="E29" s="14">
+        <v>180</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>170</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" si="12"/>
+        <v>1440</v>
+      </c>
+      <c r="J29" s="15">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
@@ -1938,14 +2184,8 @@
       <c r="F30" s="14"/>
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
@@ -1960,14 +2200,8 @@
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
       <c r="K31" s="16"/>
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
@@ -2819,11 +3053,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="12">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="14">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="13">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="15">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2841,11 +3075,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2863,11 +3097,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2885,11 +3119,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2907,11 +3141,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2929,11 +3163,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2951,11 +3185,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2973,11 +3207,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2995,11 +3229,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3017,11 +3251,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3039,11 +3273,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3061,11 +3295,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3083,11 +3317,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3105,11 +3339,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3127,11 +3361,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3149,11 +3383,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3171,11 +3405,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3193,11 +3427,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3215,11 +3449,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3237,11 +3471,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3259,11 +3493,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3281,11 +3515,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3303,11 +3537,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3325,11 +3559,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3347,11 +3581,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3369,11 +3603,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3391,11 +3625,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3413,11 +3647,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3435,11 +3669,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3457,11 +3691,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3479,11 +3713,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3501,11 +3735,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3523,11 +3757,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3545,11 +3779,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3567,11 +3801,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3589,11 +3823,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3611,11 +3845,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3633,11 +3867,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3655,11 +3889,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3677,11 +3911,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3699,11 +3933,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3721,11 +3955,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3743,11 +3977,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3765,11 +3999,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3787,11 +4021,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3809,11 +4043,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3831,11 +4065,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3853,11 +4087,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3875,11 +4109,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3897,11 +4131,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3919,11 +4153,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3941,11 +4175,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3963,11 +4197,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3985,11 +4219,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4007,11 +4241,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4029,11 +4263,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4051,11 +4285,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4073,11 +4307,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4095,11 +4329,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4117,11 +4351,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4139,11 +4373,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4161,11 +4395,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4183,11 +4417,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4205,11 +4439,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4227,11 +4461,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="14">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="16">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="15">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="17">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4249,11 +4483,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4271,11 +4505,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4293,11 +4527,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4315,11 +4549,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4337,11 +4571,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4359,11 +4593,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4381,11 +4615,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4403,11 +4637,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4425,11 +4659,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4447,11 +4681,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4469,11 +4703,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4491,11 +4725,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4513,11 +4747,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4535,11 +4769,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4557,11 +4791,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4579,11 +4813,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4601,11 +4835,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4623,11 +4857,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4645,11 +4879,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4667,11 +4901,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4689,11 +4923,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4711,11 +4945,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4733,11 +4967,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4755,11 +4989,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4777,11 +5011,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4799,11 +5033,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4821,11 +5055,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4843,11 +5077,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4865,11 +5099,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4887,11 +5121,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4909,11 +5143,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4931,11 +5165,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4953,11 +5187,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4975,11 +5209,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4997,11 +5231,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5019,11 +5253,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5041,11 +5275,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5063,11 +5297,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5085,11 +5319,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5107,11 +5341,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5129,11 +5363,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5151,11 +5385,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5173,11 +5407,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5195,11 +5429,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5217,11 +5451,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5239,11 +5473,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5261,11 +5495,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5283,11 +5517,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5305,11 +5539,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5327,11 +5561,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5349,11 +5583,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5371,11 +5605,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5393,11 +5627,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5415,11 +5649,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5437,11 +5671,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5459,11 +5693,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5481,11 +5715,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5503,11 +5737,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5525,11 +5759,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5547,11 +5781,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5569,11 +5803,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5591,11 +5825,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5613,11 +5847,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5635,11 +5869,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="16">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="18">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="17">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="19">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5657,11 +5891,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5679,11 +5913,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5701,11 +5935,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5723,11 +5957,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5745,11 +5979,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5767,11 +6001,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5789,11 +6023,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5811,11 +6045,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5833,11 +6067,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5855,11 +6089,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5877,11 +6111,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5899,11 +6133,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5921,11 +6155,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5943,11 +6177,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5965,11 +6199,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5987,11 +6221,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6009,11 +6243,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6031,11 +6265,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6053,11 +6287,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6075,11 +6309,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6097,11 +6331,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6119,11 +6353,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6141,11 +6375,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6163,11 +6397,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6185,11 +6419,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6207,11 +6441,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6229,11 +6463,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6251,11 +6485,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6273,11 +6507,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6295,11 +6529,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6317,11 +6551,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6339,11 +6573,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6361,11 +6595,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6383,11 +6617,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6405,11 +6639,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6427,11 +6661,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6449,11 +6683,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6471,11 +6705,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6493,11 +6727,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6515,11 +6749,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6537,11 +6771,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6559,11 +6793,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6581,11 +6815,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6603,11 +6837,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6625,11 +6859,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6647,11 +6881,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6669,11 +6903,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6691,11 +6925,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6713,11 +6947,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6735,11 +6969,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6757,11 +6991,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6779,11 +7013,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6801,11 +7035,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6823,11 +7057,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6845,11 +7079,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6867,11 +7101,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6889,11 +7123,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6911,11 +7145,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6933,11 +7167,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6955,11 +7189,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6977,11 +7211,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6999,11 +7233,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7021,11 +7255,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7043,11 +7277,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="18">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="20">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="19">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="21">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7065,11 +7299,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7087,11 +7321,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7109,11 +7343,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7131,11 +7365,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7153,11 +7387,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7175,11 +7409,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7197,11 +7431,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7219,11 +7453,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7241,11 +7475,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7263,11 +7497,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7285,11 +7519,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7307,11 +7541,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7329,11 +7563,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7351,11 +7585,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7373,11 +7607,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7395,11 +7629,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7417,11 +7651,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7439,11 +7673,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7461,11 +7695,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7483,11 +7717,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7505,11 +7739,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7527,11 +7761,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7549,11 +7783,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7571,11 +7805,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7593,11 +7827,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7615,11 +7849,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7637,11 +7871,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7659,11 +7893,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7681,11 +7915,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7703,11 +7937,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7725,11 +7959,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7747,11 +7981,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7769,11 +8003,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7791,11 +8025,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7813,11 +8047,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7835,11 +8069,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7857,11 +8091,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7879,11 +8113,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7901,11 +8135,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7923,11 +8157,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7945,11 +8179,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7967,11 +8201,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7989,11 +8223,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8011,11 +8245,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8033,11 +8267,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8055,11 +8289,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8077,11 +8311,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8099,11 +8333,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8121,11 +8355,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8143,11 +8377,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8165,11 +8399,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8187,11 +8421,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8209,11 +8443,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8231,11 +8465,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8253,11 +8487,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8275,11 +8509,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8297,11 +8531,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8319,11 +8553,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8341,11 +8575,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8363,11 +8597,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8385,11 +8619,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8407,11 +8641,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8429,11 +8663,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8451,11 +8685,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="20">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="22">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="21">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="23">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8473,11 +8707,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8495,11 +8729,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8517,11 +8751,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8539,11 +8773,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8561,11 +8795,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8583,11 +8817,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8605,11 +8839,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8627,11 +8861,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8649,11 +8883,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8671,11 +8905,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8693,11 +8927,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8715,11 +8949,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8737,11 +8971,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8759,11 +8993,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8781,11 +9015,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8803,11 +9037,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8825,11 +9059,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8847,11 +9081,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8869,11 +9103,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8891,11 +9125,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8913,11 +9147,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8935,11 +9169,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8957,11 +9191,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8979,11 +9213,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9001,11 +9235,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9023,11 +9257,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9045,11 +9279,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9067,11 +9301,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9089,11 +9323,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9111,11 +9345,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9133,11 +9367,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9155,11 +9389,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9177,11 +9411,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9199,11 +9433,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9221,11 +9455,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9243,11 +9477,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9265,11 +9499,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9287,11 +9521,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9309,11 +9543,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9331,11 +9565,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9353,11 +9587,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9375,11 +9609,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9397,11 +9631,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9419,11 +9653,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9441,11 +9675,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9463,11 +9697,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9485,11 +9719,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9507,11 +9741,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9529,11 +9763,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9551,11 +9785,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9573,11 +9807,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9595,11 +9829,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9617,11 +9851,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9639,11 +9873,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9661,11 +9895,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9683,11 +9917,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9705,11 +9939,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9727,11 +9961,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9749,11 +9983,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9771,11 +10005,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9793,11 +10027,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9815,11 +10049,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9837,11 +10071,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9859,11 +10093,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="22">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="24">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="23">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="25">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9881,11 +10115,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9903,11 +10137,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9925,11 +10159,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9947,11 +10181,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9969,11 +10203,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9991,11 +10225,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10013,11 +10247,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10035,11 +10269,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10057,11 +10291,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10079,11 +10313,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10101,11 +10335,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/Project Dataset.xlsx
+++ b/Project Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivam\OneDrive\Documents\0. MCA\Term - 1\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93F9788-FDFB-45F2-A2EE-70C189DD5831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B27635-7D00-40DB-937D-ABECE75FC1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,24 @@
   </si>
   <si>
     <t>Sepetember</t>
+  </si>
+  <si>
+    <t>Celebrated Ganesh Chaturthi.</t>
+  </si>
+  <si>
+    <t>Had a CA.</t>
+  </si>
+  <si>
+    <t>Solved a good set of SQL queries.</t>
+  </si>
+  <si>
+    <t>Busy day.</t>
+  </si>
+  <si>
+    <t>Had a good meal.</t>
+  </si>
+  <si>
+    <t>Weekends r about to end.</t>
   </si>
 </sst>
 </file>
@@ -1787,11 +1805,11 @@
         <v>180</v>
       </c>
       <c r="I21" s="15">
-        <f t="shared" ref="I21:I31" si="12">IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
+        <f t="shared" ref="I21:I29" si="12">IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
         <v>1440</v>
       </c>
       <c r="J21" s="15">
-        <f t="shared" ref="J21:J31" si="13">IF(I21="","",1440-I21)</f>
+        <f t="shared" ref="J21:J29" si="13">IF(I21="","",1440-I21)</f>
         <v>0</v>
       </c>
       <c r="K21" s="16" t="s">
@@ -2163,137 +2181,293 @@
         <v>0</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N29" s="17" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="14">
+        <v>300</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>300</v>
+      </c>
+      <c r="E30" s="14">
+        <v>180</v>
+      </c>
+      <c r="F30" s="14">
+        <v>450</v>
+      </c>
+      <c r="G30" s="14">
+        <v>7</v>
+      </c>
+      <c r="H30" s="14">
+        <v>180</v>
+      </c>
+      <c r="I30" s="15">
+        <f t="shared" ref="I30:I35" si="14">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
+        <v>1440</v>
+      </c>
+      <c r="J30" s="15">
+        <f t="shared" ref="J30:J35" si="15">IF(I30="","",1440-I30)</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+      <c r="A31" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="14">
+        <v>360</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>300</v>
+      </c>
+      <c r="E31" s="14">
+        <v>180</v>
+      </c>
+      <c r="F31" s="14">
+        <v>360</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>210</v>
+      </c>
+      <c r="I31" s="15">
+        <f t="shared" si="14"/>
+        <v>1440</v>
+      </c>
+      <c r="J31" s="15">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+      <c r="A32" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B32" s="14">
+        <v>600</v>
+      </c>
+      <c r="C32" s="14">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14">
+        <v>350</v>
+      </c>
+      <c r="E32" s="14">
+        <v>180</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>280</v>
+      </c>
+      <c r="I32" s="15">
+        <f t="shared" si="14"/>
+        <v>1440</v>
+      </c>
+      <c r="J32" s="15">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+      <c r="A33" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B33" s="14">
+        <v>600</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>330</v>
+      </c>
+      <c r="E33" s="14">
+        <v>180</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>300</v>
+      </c>
+      <c r="I33" s="15">
+        <f t="shared" si="14"/>
+        <v>1440</v>
+      </c>
+      <c r="J33" s="15">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+      <c r="A34" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B34" s="14">
+        <v>460</v>
+      </c>
+      <c r="C34" s="14">
+        <v>30</v>
+      </c>
+      <c r="D34" s="14">
+        <v>360</v>
+      </c>
+      <c r="E34" s="14">
+        <v>180</v>
+      </c>
+      <c r="F34" s="14">
+        <v>200</v>
+      </c>
+      <c r="G34" s="14">
+        <v>3</v>
+      </c>
+      <c r="H34" s="14">
+        <v>210</v>
+      </c>
+      <c r="I34" s="15">
+        <f t="shared" si="14"/>
+        <v>1440</v>
+      </c>
+      <c r="J34" s="15">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+      <c r="A35" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B35" s="14">
+        <v>400</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>360</v>
+      </c>
+      <c r="E35" s="14">
+        <v>180</v>
+      </c>
+      <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
+        <v>5</v>
+      </c>
+      <c r="H35" s="14">
+        <v>170</v>
+      </c>
+      <c r="I35" s="15">
+        <f t="shared" si="14"/>
+        <v>1440</v>
+      </c>
+      <c r="J35" s="15">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>
@@ -3053,11 +3227,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="14">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="16">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="15">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="17">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3075,11 +3249,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3097,11 +3271,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3119,11 +3293,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3141,11 +3315,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3163,11 +3337,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3185,11 +3359,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3207,11 +3381,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3229,11 +3403,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3251,11 +3425,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3273,11 +3447,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3295,11 +3469,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3317,11 +3491,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3339,11 +3513,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3361,11 +3535,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3383,11 +3557,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3405,11 +3579,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3427,11 +3601,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3449,11 +3623,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3471,11 +3645,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3493,11 +3667,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3515,11 +3689,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3537,11 +3711,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3559,11 +3733,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3581,11 +3755,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3603,11 +3777,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3625,11 +3799,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3647,11 +3821,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3669,11 +3843,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3691,11 +3865,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3713,11 +3887,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3735,11 +3909,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3757,11 +3931,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3779,11 +3953,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3801,11 +3975,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3823,11 +3997,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3845,11 +4019,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3867,11 +4041,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3889,11 +4063,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3911,11 +4085,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3933,11 +4107,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3955,11 +4129,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3977,11 +4151,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3999,11 +4173,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4021,11 +4195,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4043,11 +4217,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4065,11 +4239,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4087,11 +4261,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4109,11 +4283,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4131,11 +4305,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4153,11 +4327,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4175,11 +4349,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4197,11 +4371,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4219,11 +4393,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4241,11 +4415,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4263,11 +4437,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4285,11 +4459,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4307,11 +4481,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4329,11 +4503,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4351,11 +4525,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4373,11 +4547,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4395,11 +4569,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4417,11 +4591,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4439,11 +4613,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4461,11 +4635,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="16">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="18">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="17">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="19">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4483,11 +4657,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4505,11 +4679,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4527,11 +4701,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4549,11 +4723,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4571,11 +4745,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4593,11 +4767,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4615,11 +4789,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4637,11 +4811,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4659,11 +4833,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4681,11 +4855,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4703,11 +4877,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4725,11 +4899,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4747,11 +4921,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4769,11 +4943,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4791,11 +4965,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4813,11 +4987,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4835,11 +5009,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4857,11 +5031,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4879,11 +5053,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4901,11 +5075,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4923,11 +5097,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4945,11 +5119,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4967,11 +5141,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4989,11 +5163,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5011,11 +5185,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5033,11 +5207,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5055,11 +5229,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5077,11 +5251,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5099,11 +5273,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5121,11 +5295,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5143,11 +5317,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5165,11 +5339,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5187,11 +5361,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5209,11 +5383,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5231,11 +5405,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5253,11 +5427,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5275,11 +5449,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5297,11 +5471,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5319,11 +5493,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5341,11 +5515,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5363,11 +5537,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5385,11 +5559,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5407,11 +5581,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5429,11 +5603,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5451,11 +5625,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5473,11 +5647,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5495,11 +5669,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5517,11 +5691,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5539,11 +5713,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5561,11 +5735,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5583,11 +5757,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5605,11 +5779,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5627,11 +5801,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5649,11 +5823,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5671,11 +5845,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5693,11 +5867,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5715,11 +5889,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5737,11 +5911,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5759,11 +5933,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5781,11 +5955,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5803,11 +5977,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5825,11 +5999,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5847,11 +6021,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5869,11 +6043,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="18">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="20">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="19">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="21">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5891,11 +6065,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5913,11 +6087,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5935,11 +6109,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5957,11 +6131,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5979,11 +6153,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6001,11 +6175,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6023,11 +6197,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6045,11 +6219,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6067,11 +6241,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6089,11 +6263,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6111,11 +6285,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6133,11 +6307,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6155,11 +6329,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6177,11 +6351,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6199,11 +6373,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6221,11 +6395,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6243,11 +6417,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6265,11 +6439,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6287,11 +6461,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6309,11 +6483,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6331,11 +6505,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6353,11 +6527,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6375,11 +6549,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6397,11 +6571,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6419,11 +6593,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6441,11 +6615,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6463,11 +6637,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6485,11 +6659,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6507,11 +6681,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6529,11 +6703,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6551,11 +6725,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6573,11 +6747,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6595,11 +6769,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6617,11 +6791,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6639,11 +6813,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6661,11 +6835,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6683,11 +6857,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6705,11 +6879,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6727,11 +6901,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6749,11 +6923,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6771,11 +6945,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6793,11 +6967,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6815,11 +6989,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6837,11 +7011,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6859,11 +7033,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6881,11 +7055,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6903,11 +7077,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6925,11 +7099,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6947,11 +7121,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6969,11 +7143,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6991,11 +7165,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7013,11 +7187,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7035,11 +7209,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7057,11 +7231,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7079,11 +7253,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7101,11 +7275,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7123,11 +7297,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7145,11 +7319,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7167,11 +7341,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7189,11 +7363,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7211,11 +7385,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7233,11 +7407,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7255,11 +7429,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7277,11 +7451,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="20">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="22">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="21">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="23">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7299,11 +7473,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7321,11 +7495,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7343,11 +7517,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7365,11 +7539,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7387,11 +7561,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7409,11 +7583,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7431,11 +7605,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7453,11 +7627,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7475,11 +7649,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7497,11 +7671,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7519,11 +7693,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7541,11 +7715,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7563,11 +7737,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7585,11 +7759,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7607,11 +7781,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7629,11 +7803,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7651,11 +7825,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7673,11 +7847,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7695,11 +7869,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7717,11 +7891,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7739,11 +7913,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7761,11 +7935,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7783,11 +7957,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7805,11 +7979,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7827,11 +8001,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7849,11 +8023,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7871,11 +8045,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7893,11 +8067,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7915,11 +8089,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7937,11 +8111,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7959,11 +8133,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7981,11 +8155,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8003,11 +8177,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8025,11 +8199,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8047,11 +8221,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8069,11 +8243,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8091,11 +8265,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8113,11 +8287,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8135,11 +8309,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8157,11 +8331,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8179,11 +8353,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8201,11 +8375,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8223,11 +8397,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8245,11 +8419,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8267,11 +8441,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8289,11 +8463,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8311,11 +8485,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8333,11 +8507,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8355,11 +8529,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8377,11 +8551,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8399,11 +8573,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8421,11 +8595,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8443,11 +8617,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8465,11 +8639,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8487,11 +8661,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8509,11 +8683,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8531,11 +8705,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8553,11 +8727,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8575,11 +8749,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8597,11 +8771,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8619,11 +8793,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8641,11 +8815,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8663,11 +8837,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8685,11 +8859,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="22">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="24">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="23">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="25">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8707,11 +8881,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8729,11 +8903,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8751,11 +8925,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8773,11 +8947,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8795,11 +8969,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8817,11 +8991,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8839,11 +9013,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8861,11 +9035,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8883,11 +9057,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8905,11 +9079,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8927,11 +9101,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8949,11 +9123,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8971,11 +9145,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8993,11 +9167,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9015,11 +9189,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9037,11 +9211,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9059,11 +9233,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9081,11 +9255,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9103,11 +9277,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9125,11 +9299,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9147,11 +9321,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9169,11 +9343,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9191,11 +9365,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9213,11 +9387,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9235,11 +9409,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9257,11 +9431,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9279,11 +9453,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9301,11 +9475,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9323,11 +9497,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9345,11 +9519,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9367,11 +9541,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9389,11 +9563,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9411,11 +9585,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9433,11 +9607,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9455,11 +9629,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9477,11 +9651,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9499,11 +9673,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9521,11 +9695,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9543,11 +9717,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9565,11 +9739,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9587,11 +9761,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9609,11 +9783,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9631,11 +9805,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9653,11 +9827,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9675,11 +9849,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9697,11 +9871,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9719,11 +9893,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9741,11 +9915,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9763,11 +9937,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9785,11 +9959,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9807,11 +9981,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9829,11 +10003,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9851,11 +10025,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9873,11 +10047,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9895,11 +10069,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9917,11 +10091,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9939,11 +10113,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9961,11 +10135,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9983,11 +10157,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10005,11 +10179,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10027,11 +10201,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10049,11 +10223,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10071,11 +10245,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10093,11 +10267,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="24">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="26">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="25">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="27">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10115,11 +10289,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10137,11 +10311,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10159,11 +10333,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10181,11 +10355,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10203,11 +10377,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10225,11 +10399,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10247,11 +10421,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10269,11 +10443,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10291,11 +10465,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10313,11 +10487,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10335,11 +10509,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/Project Dataset.xlsx
+++ b/Project Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivam\OneDrive\Documents\0. MCA\Term - 1\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B27635-7D00-40DB-937D-ABECE75FC1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7272E2-5A5B-4015-894F-2C37A9C664D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,33 @@
   </si>
   <si>
     <t>Weekends r about to end.</t>
+  </si>
+  <si>
+    <t>Regular day. Had classes and got some time to work on my own stuff.</t>
+  </si>
+  <si>
+    <t>Classes took up most of the day. Didn't get much time for anything else.</t>
+  </si>
+  <si>
+    <t>Had a decent day. Managed to solve a few problems after classes.</t>
+  </si>
+  <si>
+    <t>Weekend started. Got a good amount of time to study and practice.</t>
+  </si>
+  <si>
+    <t>Sunday was quite busy, but still managed to get some work done.</t>
+  </si>
+  <si>
+    <t>Back to classes after the weekend. Felt a bit tired by the end of the day.</t>
+  </si>
+  <si>
+    <t>Had a normal day. Continued with LeetCode and some SQL practice.</t>
+  </si>
+  <si>
+    <t>Got some good study time today and made decent progress.</t>
+  </si>
+  <si>
+    <t>Busy day but managed to keep up with my routine.</t>
   </si>
 </sst>
 </file>
@@ -2470,202 +2497,400 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+      <c r="A36" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B36" s="14">
+        <v>360</v>
+      </c>
+      <c r="C36" s="14">
+        <v>30</v>
+      </c>
+      <c r="D36" s="14">
+        <v>300</v>
+      </c>
+      <c r="E36" s="14">
+        <v>180</v>
+      </c>
+      <c r="F36" s="14">
+        <v>450</v>
+      </c>
+      <c r="G36" s="14">
+        <v>7</v>
+      </c>
+      <c r="H36" s="14">
+        <v>120</v>
+      </c>
+      <c r="I36" s="15">
+        <v>1440</v>
+      </c>
+      <c r="J36" s="15">
+        <v>0</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+      <c r="A37" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B37" s="14">
+        <v>400</v>
+      </c>
+      <c r="C37" s="14">
+        <v>30</v>
+      </c>
+      <c r="D37" s="14">
+        <v>360</v>
+      </c>
+      <c r="E37" s="14">
+        <v>180</v>
+      </c>
+      <c r="F37" s="14">
+        <v>360</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>105</v>
+      </c>
+      <c r="I37" s="15">
+        <v>1440</v>
+      </c>
+      <c r="J37" s="15">
+        <v>0</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+      <c r="A38" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B38" s="14">
+        <v>300</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
+      <c r="D38" s="14">
+        <v>300</v>
+      </c>
+      <c r="E38" s="14">
+        <v>180</v>
+      </c>
+      <c r="F38" s="14">
+        <v>450</v>
+      </c>
+      <c r="G38" s="14">
+        <v>7</v>
+      </c>
+      <c r="H38" s="14">
+        <v>180</v>
+      </c>
+      <c r="I38" s="15">
+        <v>1440</v>
+      </c>
+      <c r="J38" s="15">
+        <v>0</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+      <c r="A39" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="14">
+        <v>600</v>
+      </c>
+      <c r="C39" s="14">
+        <v>30</v>
+      </c>
+      <c r="D39" s="14">
+        <v>360</v>
+      </c>
+      <c r="E39" s="14">
+        <v>180</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>270</v>
+      </c>
+      <c r="I39" s="15">
+        <v>1440</v>
+      </c>
+      <c r="J39" s="15">
+        <v>0</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+      <c r="A40" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B40" s="14">
+        <v>600</v>
+      </c>
+      <c r="C40" s="14">
+        <v>30</v>
+      </c>
+      <c r="D40" s="14">
+        <v>330</v>
+      </c>
+      <c r="E40" s="14">
+        <v>180</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>300</v>
+      </c>
+      <c r="I40" s="15">
+        <v>1440</v>
+      </c>
+      <c r="J40" s="15">
+        <v>0</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+      <c r="A41" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="14">
+        <v>360</v>
+      </c>
+      <c r="C41" s="14">
+        <v>30</v>
+      </c>
+      <c r="D41" s="14">
+        <v>360</v>
+      </c>
+      <c r="E41" s="14">
+        <v>180</v>
+      </c>
+      <c r="F41" s="14">
+        <v>360</v>
+      </c>
+      <c r="G41" s="14">
+        <v>5</v>
+      </c>
+      <c r="H41" s="14">
+        <v>150</v>
+      </c>
+      <c r="I41" s="15">
+        <v>1440</v>
+      </c>
+      <c r="J41" s="15">
+        <v>0</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B42" s="14">
+        <v>300</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
+      <c r="D42" s="14">
+        <v>300</v>
+      </c>
+      <c r="E42" s="14">
+        <v>180</v>
+      </c>
+      <c r="F42" s="14">
+        <v>450</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>180</v>
+      </c>
+      <c r="I42" s="15">
+        <v>1440</v>
+      </c>
+      <c r="J42" s="15">
+        <v>0</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+      <c r="A43" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="14">
+        <v>400</v>
+      </c>
+      <c r="C43" s="14">
+        <v>30</v>
+      </c>
+      <c r="D43" s="14">
+        <v>360</v>
+      </c>
+      <c r="E43" s="14">
+        <v>120</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>4</v>
+      </c>
+      <c r="H43" s="14">
+        <v>230</v>
+      </c>
+      <c r="I43" s="15">
+        <v>1440</v>
+      </c>
+      <c r="J43" s="15">
+        <v>0</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+      <c r="A44" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B44" s="14">
+        <v>360</v>
+      </c>
+      <c r="C44" s="14">
+        <v>30</v>
+      </c>
+      <c r="D44" s="14">
+        <v>300</v>
+      </c>
+      <c r="E44" s="14">
+        <v>180</v>
+      </c>
+      <c r="F44" s="14">
+        <v>450</v>
+      </c>
+      <c r="G44" s="14">
+        <v>7</v>
+      </c>
+      <c r="H44" s="14">
+        <v>120</v>
+      </c>
+      <c r="I44" s="15">
+        <v>1440</v>
+      </c>
+      <c r="J44" s="15">
+        <v>0</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
@@ -10550,6 +10775,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Project Dataset.xlsx
+++ b/Project Dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivam\OneDrive\Documents\0. MCA\Term - 1\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7272E2-5A5B-4015-894F-2C37A9C664D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AF43E6-3E16-46A2-B022-8C4C8E5490E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -199,9 +199,6 @@
     <t>5. GOOD PRACTICE</t>
   </si>
   <si>
-    <t>Shivam Kumar Signh</t>
-  </si>
-  <si>
     <t>CAP-776</t>
   </si>
   <si>
@@ -338,6 +335,9 @@
   </si>
   <si>
     <t>Busy day but managed to keep up with my routine.</t>
+  </si>
+  <si>
+    <t>Shivam Kumar Singh</t>
   </si>
 </sst>
 </file>
@@ -988,7 +988,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N402"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1025,7 +1025,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -1042,7 +1042,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1050,7 +1050,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1142,11 +1142,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I70" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J70" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1164,56 +1164,56 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B7" s="14">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="C7" s="14">
         <v>30</v>
       </c>
       <c r="D7" s="14">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="E7" s="14">
         <v>180</v>
       </c>
       <c r="F7" s="14">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="G7" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H7" s="14">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I7" si="2">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>1440</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J7" si="3">IF(I7="","",1440-I7)</f>
         <v>0</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B8" s="14">
-        <v>570</v>
+        <v>480</v>
       </c>
       <c r="C8" s="14">
         <v>30</v>
@@ -1225,13 +1225,13 @@
         <v>180</v>
       </c>
       <c r="F8" s="14">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="G8" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H8" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
@@ -1242,39 +1242,39 @@
         <v>0</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L8" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B9" s="14">
-        <v>300</v>
+        <v>570</v>
       </c>
       <c r="C9" s="14">
         <v>30</v>
       </c>
       <c r="D9" s="14">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="E9" s="14">
         <v>180</v>
       </c>
       <c r="F9" s="14">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="G9" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H9" s="14">
         <v>120</v>
@@ -1294,36 +1294,36 @@
         <v>50</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B10" s="14">
+        <v>300</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
         <v>360</v>
-      </c>
-      <c r="C10" s="14">
-        <v>45</v>
-      </c>
-      <c r="D10" s="14">
-        <v>300</v>
       </c>
       <c r="E10" s="14">
         <v>180</v>
       </c>
       <c r="F10" s="14">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="G10" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H10" s="14">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
@@ -1340,36 +1340,36 @@
         <v>50</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="B11" s="14">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="C11" s="14">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D11" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E11" s="14">
         <v>180</v>
       </c>
       <c r="F11" s="14">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="G11" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H11" s="14">
-        <v>290</v>
+        <v>195</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
@@ -1380,21 +1380,21 @@
         <v>0</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="B12" s="14">
         <v>600</v>
@@ -1426,27 +1426,27 @@
         <v>0</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="B13" s="14">
-        <v>470</v>
+        <v>600</v>
       </c>
       <c r="C13" s="14">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D13" s="14">
         <v>360</v>
@@ -1455,13 +1455,13 @@
         <v>180</v>
       </c>
       <c r="F13" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G13" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13" s="14">
-        <v>200</v>
+        <v>290</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
@@ -1472,42 +1472,42 @@
         <v>0</v>
       </c>
       <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L13" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="M13" s="16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B14" s="14">
-        <v>360</v>
+        <v>470</v>
       </c>
       <c r="C14" s="14">
         <v>30</v>
       </c>
       <c r="D14" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="E14" s="14">
         <v>180</v>
       </c>
       <c r="F14" s="14">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="G14" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H14" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
@@ -1518,24 +1518,24 @@
         <v>0</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B15" s="14">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="C15" s="14">
         <v>30</v>
@@ -1544,62 +1544,62 @@
         <v>300</v>
       </c>
       <c r="E15" s="14">
+        <v>180</v>
+      </c>
+      <c r="F15" s="14">
+        <v>450</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
         <v>120</v>
       </c>
-      <c r="F15" s="14">
-        <v>300</v>
-      </c>
-      <c r="G15" s="14">
-        <v>4</v>
-      </c>
-      <c r="H15" s="14">
-        <v>190</v>
-      </c>
       <c r="I15" s="15">
-        <f t="shared" ref="I15" si="2">IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
+        <f t="shared" si="0"/>
         <v>1440</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" ref="J15" si="3">IF(I15="","",1440-I15)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N15" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L15" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B16" s="14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C16" s="14">
         <v>30</v>
       </c>
       <c r="D16" s="14">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="E16" s="14">
         <v>120</v>
       </c>
       <c r="F16" s="14">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H16" s="14">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" ref="I16" si="4">IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
@@ -1610,39 +1610,39 @@
         <v>0</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B17" s="14">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="C17" s="14">
         <v>30</v>
       </c>
       <c r="D17" s="14">
-        <v>370</v>
+        <v>240</v>
       </c>
       <c r="E17" s="14">
         <v>120</v>
       </c>
       <c r="F17" s="14">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="G17" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H17" s="14">
         <v>200</v>
@@ -1656,21 +1656,21 @@
         <v>0</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B18" s="14">
         <v>600</v>
@@ -1679,44 +1679,44 @@
         <v>30</v>
       </c>
       <c r="D18" s="14">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="E18" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="F18" s="14">
+        <v>120</v>
+      </c>
+      <c r="G18" s="14">
+        <v>2</v>
+      </c>
+      <c r="H18" s="14">
+        <v>200</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" ref="I18" si="8">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
+        <v>1440</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" ref="J18" si="9">IF(I18="","",1440-I18)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="14">
-        <v>0</v>
-      </c>
-      <c r="H18" s="14">
-        <v>330</v>
-      </c>
-      <c r="I18" s="15">
-        <f t="shared" ref="I18:I19" si="8">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
-        <v>1440</v>
-      </c>
-      <c r="J18" s="15">
-        <f t="shared" ref="J18:J19" si="9">IF(I18="","",1440-I18)</f>
-        <v>0</v>
-      </c>
       <c r="K18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L18" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L18" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="M18" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B19" s="14">
         <v>600</v>
@@ -1725,7 +1725,7 @@
         <v>30</v>
       </c>
       <c r="D19" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E19" s="14">
         <v>180</v>
@@ -1737,127 +1737,127 @@
         <v>0</v>
       </c>
       <c r="H19" s="14">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="I19" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I19:I20" si="10">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
         <v>1440</v>
       </c>
       <c r="J19" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J19:J20" si="11">IF(I19="","",1440-I19)</f>
         <v>0</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B20" s="14">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="C20" s="14">
         <v>30</v>
       </c>
       <c r="D20" s="14">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="E20" s="14">
         <v>180</v>
       </c>
       <c r="F20" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H20" s="14">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="I20" s="15">
-        <f t="shared" ref="I20" si="10">IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
+        <f t="shared" si="10"/>
         <v>1440</v>
       </c>
       <c r="J20" s="15">
-        <f t="shared" ref="J20" si="11">IF(I20="","",1440-I20)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B21" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C21" s="14">
         <v>30</v>
       </c>
       <c r="D21" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="E21" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="F21" s="14">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="G21" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H21" s="14">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="I21" s="15">
-        <f t="shared" ref="I21:I29" si="12">IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
+        <f t="shared" ref="I21" si="12">IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
         <v>1440</v>
       </c>
       <c r="J21" s="15">
-        <f t="shared" ref="J21:J29" si="13">IF(I21="","",1440-I21)</f>
+        <f t="shared" ref="J21" si="13">IF(I21="","",1440-I21)</f>
         <v>0</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L21" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B22" s="14">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="C22" s="14">
         <v>30</v>
@@ -1869,41 +1869,41 @@
         <v>120</v>
       </c>
       <c r="F22" s="14">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H22" s="14">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="I22" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I22:I30" si="14">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
         <v>1440</v>
       </c>
       <c r="J22" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J22:J30" si="15">IF(I22="","",1440-I22)</f>
         <v>0</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B23" s="14">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="C23" s="14">
         <v>30</v>
@@ -1912,44 +1912,44 @@
         <v>300</v>
       </c>
       <c r="E23" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="F23" s="14">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H23" s="14">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I23" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1440</v>
       </c>
       <c r="J23" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B24" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="C24" s="14">
         <v>30</v>
@@ -1958,44 +1958,44 @@
         <v>300</v>
       </c>
       <c r="E24" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="F24" s="14">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="G24" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H24" s="14">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="I24" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1440</v>
       </c>
       <c r="J24" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B25" s="14">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="C25" s="14">
         <v>30</v>
@@ -2004,41 +2004,41 @@
         <v>300</v>
       </c>
       <c r="E25" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="F25" s="14">
+        <v>360</v>
+      </c>
+      <c r="G25" s="14">
+        <v>5</v>
+      </c>
+      <c r="H25" s="14">
+        <v>230</v>
+      </c>
+      <c r="I25" s="15">
+        <f t="shared" si="14"/>
+        <v>1440</v>
+      </c>
+      <c r="J25" s="15">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="G25" s="14">
-        <v>0</v>
-      </c>
-      <c r="H25" s="14">
-        <v>330</v>
-      </c>
-      <c r="I25" s="15">
-        <f t="shared" si="12"/>
-        <v>1440</v>
-      </c>
-      <c r="J25" s="15">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
       <c r="K25" s="16" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B26" s="14">
         <v>600</v>
@@ -2047,7 +2047,7 @@
         <v>30</v>
       </c>
       <c r="D26" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E26" s="14">
         <v>180</v>
@@ -2059,78 +2059,78 @@
         <v>0</v>
       </c>
       <c r="H26" s="14">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="I26" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1440</v>
       </c>
       <c r="J26" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K26" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L26" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L26" s="16" t="s">
-        <v>63</v>
-      </c>
       <c r="M26" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B27" s="14">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="C27" s="14">
         <v>30</v>
       </c>
       <c r="D27" s="14">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="E27" s="14">
         <v>180</v>
       </c>
       <c r="F27" s="14">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H27" s="14">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="I27" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1440</v>
       </c>
       <c r="J27" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B28" s="14">
         <v>300</v>
@@ -2139,139 +2139,139 @@
         <v>30</v>
       </c>
       <c r="D28" s="14">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="E28" s="14">
         <v>180</v>
       </c>
       <c r="F28" s="14">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="I28" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1440</v>
       </c>
       <c r="J28" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L28" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B29" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C29" s="14">
         <v>30</v>
       </c>
       <c r="D29" s="14">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="E29" s="14">
         <v>180</v>
       </c>
       <c r="F29" s="14">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H29" s="14">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="I29" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1440</v>
       </c>
       <c r="J29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="L29" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B30" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C30" s="14">
         <v>30</v>
       </c>
       <c r="D30" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E30" s="14">
         <v>180</v>
       </c>
       <c r="F30" s="14">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="G30" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H30" s="14">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" ref="I30:I35" si="14">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
+        <f t="shared" si="14"/>
         <v>1440</v>
       </c>
       <c r="J30" s="15">
-        <f t="shared" ref="J30:J35" si="15">IF(I30="","",1440-I30)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B31" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C31" s="14">
         <v>30</v>
@@ -2283,84 +2283,84 @@
         <v>180</v>
       </c>
       <c r="F31" s="14">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="G31" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H31" s="14">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="I31" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="I31:I36" si="16">IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
         <v>1440</v>
       </c>
       <c r="J31" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="J31:J36" si="17">IF(I31="","",1440-I31)</f>
         <v>0</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B32" s="14">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="C32" s="14">
         <v>30</v>
       </c>
       <c r="D32" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="E32" s="14">
         <v>180</v>
       </c>
       <c r="F32" s="14">
+        <v>360</v>
+      </c>
+      <c r="G32" s="14">
+        <v>5</v>
+      </c>
+      <c r="H32" s="14">
+        <v>210</v>
+      </c>
+      <c r="I32" s="15">
+        <f t="shared" si="16"/>
+        <v>1440</v>
+      </c>
+      <c r="J32" s="15">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G32" s="14">
-        <v>0</v>
-      </c>
-      <c r="H32" s="14">
-        <v>280</v>
-      </c>
-      <c r="I32" s="15">
-        <f t="shared" si="14"/>
-        <v>1440</v>
-      </c>
-      <c r="J32" s="15">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
       <c r="K32" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B33" s="14">
         <v>600</v>
@@ -2369,7 +2369,7 @@
         <v>30</v>
       </c>
       <c r="D33" s="14">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="E33" s="14">
         <v>180</v>
@@ -2381,81 +2381,81 @@
         <v>0</v>
       </c>
       <c r="H33" s="14">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="I33" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1440</v>
       </c>
       <c r="J33" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B34" s="14">
-        <v>460</v>
+        <v>600</v>
       </c>
       <c r="C34" s="14">
         <v>30</v>
       </c>
       <c r="D34" s="14">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="E34" s="14">
         <v>180</v>
       </c>
       <c r="F34" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G34" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H34" s="14">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="I34" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1440</v>
       </c>
       <c r="J34" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B35" s="14">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="C35" s="14">
         <v>30</v>
@@ -2467,103 +2467,105 @@
         <v>180</v>
       </c>
       <c r="F35" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G35" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H35" s="14">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="I35" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1440</v>
       </c>
       <c r="J35" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B36" s="14">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="C36" s="14">
         <v>30</v>
       </c>
       <c r="D36" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="E36" s="14">
         <v>180</v>
       </c>
       <c r="F36" s="14">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="G36" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H36" s="14">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="I36" s="15">
+        <f t="shared" si="16"/>
         <v>1440</v>
       </c>
       <c r="J36" s="15">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="M36" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="13">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B37" s="14">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="C37" s="14">
         <v>30</v>
       </c>
       <c r="D37" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E37" s="14">
         <v>180</v>
       </c>
       <c r="F37" s="14">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="G37" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H37" s="14">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="I37" s="15">
         <v>1440</v>
@@ -2572,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L37" s="16" t="s">
         <v>50</v>
@@ -2581,33 +2583,33 @@
         <v>51</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="13">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B38" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C38" s="14">
         <v>30</v>
       </c>
       <c r="D38" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="E38" s="14">
         <v>180</v>
       </c>
       <c r="F38" s="14">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="G38" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H38" s="14">
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="I38" s="15">
         <v>1440</v>
@@ -2616,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L38" s="16" t="s">
         <v>50</v>
@@ -2625,33 +2627,33 @@
         <v>51</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="13">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B39" s="14">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="C39" s="14">
         <v>30</v>
       </c>
       <c r="D39" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E39" s="14">
         <v>180</v>
       </c>
       <c r="F39" s="14">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="G39" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H39" s="14">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="I39" s="15">
         <v>1440</v>
@@ -2660,21 +2662,21 @@
         <v>0</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="13">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B40" s="14">
         <v>600</v>
@@ -2683,7 +2685,7 @@
         <v>30</v>
       </c>
       <c r="D40" s="14">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="E40" s="14">
         <v>180</v>
@@ -2695,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="14">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="I40" s="15">
         <v>1440</v>
@@ -2704,42 +2706,42 @@
         <v>0</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="13">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B41" s="14">
-        <v>360</v>
+        <v>600</v>
       </c>
       <c r="C41" s="14">
         <v>30</v>
       </c>
       <c r="D41" s="14">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="E41" s="14">
         <v>180</v>
       </c>
       <c r="F41" s="14">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="G41" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H41" s="14">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="I41" s="15">
         <v>1440</v>
@@ -2748,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L41" s="16" t="s">
         <v>50</v>
@@ -2757,33 +2759,33 @@
         <v>51</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="13">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B42" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C42" s="14">
         <v>30</v>
       </c>
       <c r="D42" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="E42" s="14">
         <v>180</v>
       </c>
       <c r="F42" s="14">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="G42" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H42" s="14">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I42" s="15">
         <v>1440</v>
@@ -2792,42 +2794,42 @@
         <v>0</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L42" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="13">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B43" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="C43" s="14">
         <v>30</v>
       </c>
       <c r="D43" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E43" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="F43" s="14">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="G43" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H43" s="14">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="I43" s="15">
         <v>1440</v>
@@ -2836,42 +2838,42 @@
         <v>0</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="13">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B44" s="14">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="C44" s="14">
         <v>30</v>
       </c>
       <c r="D44" s="14">
+        <v>360</v>
+      </c>
+      <c r="E44" s="14">
+        <v>120</v>
+      </c>
+      <c r="F44" s="14">
         <v>300</v>
       </c>
-      <c r="E44" s="14">
-        <v>180</v>
-      </c>
-      <c r="F44" s="14">
-        <v>450</v>
-      </c>
       <c r="G44" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H44" s="14">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="I44" s="15">
         <v>1440</v>
@@ -2880,39 +2882,61 @@
         <v>0</v>
       </c>
       <c r="K44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B45" s="14">
+        <v>360</v>
+      </c>
+      <c r="C45" s="14">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14">
+        <v>300</v>
+      </c>
+      <c r="E45" s="14">
+        <v>180</v>
+      </c>
+      <c r="F45" s="14">
+        <v>450</v>
+      </c>
+      <c r="G45" s="14">
+        <v>7</v>
+      </c>
+      <c r="H45" s="14">
+        <v>120</v>
+      </c>
+      <c r="I45" s="15">
+        <v>1440</v>
+      </c>
+      <c r="J45" s="15">
+        <v>0</v>
+      </c>
+      <c r="K45" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L44" s="16" t="s">
+      <c r="L45" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M44" s="16" t="s">
+      <c r="M45" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N44" s="17" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+      <c r="N45" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
@@ -3452,11 +3476,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="16">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="17">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3474,11 +3498,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="I71:I134" si="18">IF(SUM(B71:F71,H71)=0,"",SUM(B71:F71,H71))</f>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="J71:J134" si="19">IF(I71="","",1440-I71)</f>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3496,11 +3520,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3518,11 +3542,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3540,11 +3564,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3562,11 +3586,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3584,11 +3608,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3606,11 +3630,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3628,11 +3652,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3650,11 +3674,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3672,11 +3696,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3694,11 +3718,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3716,11 +3740,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3738,11 +3762,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3760,11 +3784,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3782,11 +3806,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3804,11 +3828,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3826,11 +3850,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3848,11 +3872,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3870,11 +3894,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3892,11 +3916,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3914,11 +3938,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3936,11 +3960,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3958,11 +3982,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3980,11 +4004,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -4002,11 +4026,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -4024,11 +4048,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -4046,11 +4070,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -4068,11 +4092,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -4090,11 +4114,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -4112,11 +4136,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -4134,11 +4158,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -4156,11 +4180,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -4178,11 +4202,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -4200,11 +4224,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -4222,11 +4246,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4244,11 +4268,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4266,11 +4290,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4288,11 +4312,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4310,11 +4334,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4332,11 +4356,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4354,11 +4378,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4376,11 +4400,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4398,11 +4422,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4420,11 +4444,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4442,11 +4466,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4464,11 +4488,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4486,11 +4510,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4508,11 +4532,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4530,11 +4554,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4552,11 +4576,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4574,11 +4598,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4596,11 +4620,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4618,11 +4642,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4640,11 +4664,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4662,11 +4686,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4684,11 +4708,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4706,11 +4730,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4728,11 +4752,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4750,11 +4774,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4772,11 +4796,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4794,11 +4818,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4816,11 +4840,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4838,11 +4862,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4860,11 +4884,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="18">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="19">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4882,11 +4906,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="I135:I198" si="20">IF(SUM(B135:F135,H135)=0,"",SUM(B135:F135,H135))</f>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="J135:J198" si="21">IF(I135="","",1440-I135)</f>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4904,11 +4928,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4926,11 +4950,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4948,11 +4972,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4970,11 +4994,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4992,11 +5016,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -5014,11 +5038,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -5036,11 +5060,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -5058,11 +5082,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -5080,11 +5104,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -5102,11 +5126,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -5124,11 +5148,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -5146,11 +5170,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -5168,11 +5192,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -5190,11 +5214,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -5212,11 +5236,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5234,11 +5258,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5256,11 +5280,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5278,11 +5302,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5300,11 +5324,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5322,11 +5346,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5344,11 +5368,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5366,11 +5390,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5388,11 +5412,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5410,11 +5434,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5432,11 +5456,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5454,11 +5478,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5476,11 +5500,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5498,11 +5522,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5520,11 +5544,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5542,11 +5566,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5564,11 +5588,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5586,11 +5610,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5608,11 +5632,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5630,11 +5654,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5652,11 +5676,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5674,11 +5698,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5696,11 +5720,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5718,11 +5742,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5740,11 +5764,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5762,11 +5786,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5784,11 +5808,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5806,11 +5830,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5828,11 +5852,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5850,11 +5874,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5872,11 +5896,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5894,11 +5918,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5916,11 +5940,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5938,11 +5962,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5960,11 +5984,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5982,11 +6006,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -6004,11 +6028,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -6026,11 +6050,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -6048,11 +6072,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -6070,11 +6094,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -6092,11 +6116,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -6114,11 +6138,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -6136,11 +6160,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -6158,11 +6182,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6180,11 +6204,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6202,11 +6226,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6224,11 +6248,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6246,11 +6270,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6268,11 +6292,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="20">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="21">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6290,11 +6314,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="I199:I262" si="22">IF(SUM(B199:F199,H199)=0,"",SUM(B199:F199,H199))</f>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="J199:J262" si="23">IF(I199="","",1440-I199)</f>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6312,11 +6336,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6334,11 +6358,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6356,11 +6380,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6378,11 +6402,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6400,11 +6424,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6422,11 +6446,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6444,11 +6468,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6466,11 +6490,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6488,11 +6512,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6510,11 +6534,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6532,11 +6556,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6554,11 +6578,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6576,11 +6600,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6598,11 +6622,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6620,11 +6644,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6642,11 +6666,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6664,11 +6688,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6686,11 +6710,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6708,11 +6732,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6730,11 +6754,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6752,11 +6776,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6774,11 +6798,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6796,11 +6820,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6818,11 +6842,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6840,11 +6864,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6862,11 +6886,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6884,11 +6908,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6906,11 +6930,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6928,11 +6952,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6950,11 +6974,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6972,11 +6996,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6994,11 +7018,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -7016,11 +7040,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -7038,11 +7062,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -7060,11 +7084,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -7082,11 +7106,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -7104,11 +7128,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -7126,11 +7150,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -7148,11 +7172,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -7170,11 +7194,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -7192,11 +7216,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -7214,11 +7238,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7236,11 +7260,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7258,11 +7282,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7280,11 +7304,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7302,11 +7326,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7324,11 +7348,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7346,11 +7370,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7368,11 +7392,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7390,11 +7414,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7412,11 +7436,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7434,11 +7458,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7456,11 +7480,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7478,11 +7502,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7500,11 +7524,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7522,11 +7546,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7544,11 +7568,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7566,11 +7590,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7588,11 +7612,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7610,11 +7634,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7632,11 +7656,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7654,11 +7678,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7676,11 +7700,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="22">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="23">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7698,11 +7722,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="I263:I326" si="24">IF(SUM(B263:F263,H263)=0,"",SUM(B263:F263,H263))</f>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="J263:J326" si="25">IF(I263="","",1440-I263)</f>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7720,11 +7744,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7742,11 +7766,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7764,11 +7788,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7786,11 +7810,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7808,11 +7832,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7830,11 +7854,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7852,11 +7876,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7874,11 +7898,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7896,11 +7920,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7918,11 +7942,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7940,11 +7964,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7962,11 +7986,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7984,11 +8008,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -8006,11 +8030,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -8028,11 +8052,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -8050,11 +8074,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -8072,11 +8096,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -8094,11 +8118,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -8116,11 +8140,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -8138,11 +8162,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -8160,11 +8184,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -8182,11 +8206,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8204,11 +8228,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -8226,11 +8250,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8248,11 +8272,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8270,11 +8294,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8292,11 +8316,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8314,11 +8338,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8336,11 +8360,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8358,11 +8382,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8380,11 +8404,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8402,11 +8426,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8424,11 +8448,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8446,11 +8470,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8468,11 +8492,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8490,11 +8514,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8512,11 +8536,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8534,11 +8558,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8556,11 +8580,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8578,11 +8602,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8600,11 +8624,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8622,11 +8646,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8644,11 +8668,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8666,11 +8690,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8688,11 +8712,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8710,11 +8734,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8732,11 +8756,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8754,11 +8778,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8776,11 +8800,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8798,11 +8822,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8820,11 +8844,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8842,11 +8866,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8864,11 +8888,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8886,11 +8910,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8908,11 +8932,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8930,11 +8954,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8952,11 +8976,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8974,11 +8998,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8996,11 +9020,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9018,11 +9042,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9040,11 +9064,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9062,11 +9086,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9084,11 +9108,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="24">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="25">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9106,11 +9130,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="I327:I390" si="26">IF(SUM(B327:F327,H327)=0,"",SUM(B327:F327,H327))</f>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="J327:J390" si="27">IF(I327="","",1440-I327)</f>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9128,11 +9152,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9150,11 +9174,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9172,11 +9196,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -9194,11 +9218,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -9216,11 +9240,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9238,11 +9262,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9260,11 +9284,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9282,11 +9306,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9304,11 +9328,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9326,11 +9350,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9348,11 +9372,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9370,11 +9394,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9392,11 +9416,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9414,11 +9438,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9436,11 +9460,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9458,11 +9482,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9480,11 +9504,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9502,11 +9526,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9524,11 +9548,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9546,11 +9570,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9568,11 +9592,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9590,11 +9614,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9612,11 +9636,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9634,11 +9658,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9656,11 +9680,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9678,11 +9702,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9700,11 +9724,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9722,11 +9746,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9744,11 +9768,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9766,11 +9790,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9788,11 +9812,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9810,11 +9834,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9832,11 +9856,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9854,11 +9878,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9876,11 +9900,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9898,11 +9922,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9920,11 +9944,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9942,11 +9966,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9964,11 +9988,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9986,11 +10010,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -10008,11 +10032,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -10030,11 +10054,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -10052,11 +10076,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -10074,11 +10098,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -10096,11 +10120,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -10118,11 +10142,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -10140,11 +10164,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -10162,11 +10186,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -10184,11 +10208,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -10206,11 +10230,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -10228,11 +10252,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10250,11 +10274,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10272,11 +10296,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10294,11 +10318,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10316,11 +10340,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10338,11 +10362,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10360,11 +10384,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10382,11 +10406,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10404,11 +10428,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10426,11 +10450,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10448,11 +10472,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10470,11 +10494,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10492,11 +10516,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="26">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="27">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10514,11 +10538,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="I391:I402" si="28">IF(SUM(B391:F391,H391)=0,"",SUM(B391:F391,H391))</f>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="J391:J402" si="29">IF(I391="","",1440-I391)</f>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10536,11 +10560,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10558,11 +10582,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10580,11 +10604,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10602,11 +10626,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10624,11 +10648,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10646,11 +10670,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10668,11 +10692,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10690,11 +10714,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10712,11 +10736,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10734,17 +10758,39 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
       <c r="L401" s="16"/>
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A402" s="13"/>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="15" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="J402" s="15" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="K402" s="16"/>
+      <c r="L402" s="16"/>
+      <c r="M402" s="16"/>
+      <c r="N402" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -10755,21 +10801,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J402">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K402" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L402" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M402" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
